--- a/GearSage-client/pkgGear/data_raw/gamakatsu_hook_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/gamakatsu_hook_import.xlsx
@@ -459,7 +459,7 @@
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>特种钩 / Antenna / Gika</v>
+        <v>特种钩</v>
       </c>
       <c r="H2" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/antenna_hook.webp</v>
@@ -494,7 +494,7 @@
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>倒钓钩 / Drop Shot</v>
+        <v>倒钓钩</v>
       </c>
       <c r="H3" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/super_tuned_drop_shot.webp</v>
@@ -529,7 +529,7 @@
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>圆钩 / Weedless Circle</v>
+        <v>圆钩</v>
       </c>
       <c r="H4" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/catfish_circle_weedless.jpg</v>
@@ -564,7 +564,7 @@
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>特种钩 / Stiletto</v>
+        <v>直柄钩</v>
       </c>
       <c r="H5" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/stiletto.jpg</v>
@@ -599,7 +599,7 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>直柄钩 / Aberdeen</v>
+        <v>直柄钩</v>
       </c>
       <c r="H6" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/sticker.jpg</v>
@@ -634,7 +634,7 @@
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>直柄钩 / Trout Stinger</v>
+        <v>直柄钩</v>
       </c>
       <c r="H7" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/trout_stinger.jpg</v>
@@ -669,7 +669,7 @@
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>挂钩 / Spin Bait</v>
+        <v>辅助挂钩</v>
       </c>
       <c r="H8" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/spin_bait.jpg</v>
@@ -704,7 +704,7 @@
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>直柄钩 / Aberdeen</v>
+        <v>直柄钩</v>
       </c>
       <c r="H9" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/aberdeen.jpg</v>
@@ -739,7 +739,7 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>倒钓钩 / Wacky Weedless</v>
+        <v>Wacky/Neko钩</v>
       </c>
       <c r="H10" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/wicked_wacky.jpg</v>
@@ -774,7 +774,7 @@
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>曲柄钩 / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H11" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/walleye_wide_gap.jpg</v>
@@ -809,7 +809,7 @@
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>直柄钩 / Trout Worm</v>
+        <v>直柄钩</v>
       </c>
       <c r="H12" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/tw_hook.jpg</v>
@@ -844,7 +844,7 @@
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>挂钩 / Trailer Hook</v>
+        <v>辅助挂钩</v>
       </c>
       <c r="H13" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/trailer_hook_sp.jpg</v>
@@ -879,7 +879,7 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>倒钓钩 / Drop Shot Weedless</v>
+        <v>倒钓钩</v>
       </c>
       <c r="H14" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/split_shot_drop_shot_weedless.jpg</v>
@@ -914,7 +914,7 @@
         <v/>
       </c>
       <c r="G15" t="str">
-        <v>倒钓钩 / Drop Shot</v>
+        <v>倒钓钩</v>
       </c>
       <c r="H15" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/split_shot_drop_shot.jpg</v>
@@ -949,7 +949,7 @@
         <v/>
       </c>
       <c r="G16" t="str">
-        <v>挂钩 / Spinnerbait Trailer</v>
+        <v>辅助挂钩</v>
       </c>
       <c r="H16" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/spinner_bait.jpg</v>
@@ -984,7 +984,7 @@
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>直柄钩 / Egg Hook / Barb on Shank</v>
+        <v>直柄钩</v>
       </c>
       <c r="H17" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/single_egg_hook_barb_on_shank.jpg</v>
@@ -1019,7 +1019,7 @@
         <v/>
       </c>
       <c r="G18" t="str">
-        <v>直柄钩 / Upturned Eye</v>
+        <v>直柄钩</v>
       </c>
       <c r="H18" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/shiner_upturned_eye.jpg</v>
@@ -1054,7 +1054,7 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>直柄钩 / Straight Eye</v>
+        <v>直柄钩</v>
       </c>
       <c r="H19" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/shiner_straight_eye.jpg</v>
@@ -1089,7 +1089,7 @@
         <v/>
       </c>
       <c r="G20" t="str">
-        <v>曲柄钩 / Micro Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H20" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/micro_wide_gap.jpg</v>
@@ -1124,7 +1124,7 @@
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>曲柄钩 / Micro V Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H21" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/micro_v_gap.jpg</v>
@@ -1159,7 +1159,7 @@
         <v/>
       </c>
       <c r="G22" t="str">
-        <v>曲柄钩 / Micro Perfect Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H22" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/micro_perfect_gap.jpg</v>
@@ -1194,7 +1194,7 @@
         <v/>
       </c>
       <c r="G23" t="str">
-        <v>挂钩 / Stinger</v>
+        <v>辅助挂钩</v>
       </c>
       <c r="H23" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/g_stinger.jpg</v>
@@ -1229,7 +1229,7 @@
         <v/>
       </c>
       <c r="G24" t="str">
-        <v>鲤鱼钩 / Super Hook</v>
+        <v>鲤鱼钩</v>
       </c>
       <c r="H24" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/g_carp_super_hook.jpg</v>
@@ -1264,7 +1264,7 @@
         <v/>
       </c>
       <c r="G25" t="str">
-        <v>鲤鱼钩 / Specialist RX</v>
+        <v>鲤鱼钩</v>
       </c>
       <c r="H25" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/g_carp_specialist_rx.jpg</v>
@@ -1299,7 +1299,7 @@
         <v/>
       </c>
       <c r="G26" t="str">
-        <v>鲤鱼钩 / Specialist R</v>
+        <v>鲤鱼钩</v>
       </c>
       <c r="H26" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/g_carp_specialist_r.jpg</v>
@@ -1334,7 +1334,7 @@
         <v/>
       </c>
       <c r="G27" t="str">
-        <v>鲤鱼钩 / Hump Back</v>
+        <v>鲤鱼钩</v>
       </c>
       <c r="H27" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/g_carp_hump_back.jpg</v>
@@ -1369,7 +1369,7 @@
         <v/>
       </c>
       <c r="G28" t="str">
-        <v>曲柄钩 / Finesse Wide Gap Weedless</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H28" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/finesse_wide_gap_weedless.jpg</v>
@@ -1404,7 +1404,7 @@
         <v/>
       </c>
       <c r="G29" t="str">
-        <v>曲柄钩 / Finesse Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H29" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/finesse_wide_gap.jpg</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="G30" t="str">
-        <v>组合钩 / Assortment</v>
+        <v>组合装</v>
       </c>
       <c r="H30" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/crappie_assortment.jpg</v>
@@ -1474,7 +1474,7 @@
         <v/>
       </c>
       <c r="G31" t="str">
-        <v>组合钩 / Assortment</v>
+        <v>组合装</v>
       </c>
       <c r="H31" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/catfish_assortment.jpg</v>
@@ -1509,7 +1509,7 @@
         <v/>
       </c>
       <c r="G32" t="str">
-        <v>圆钩 / Big Cat Circle</v>
+        <v>圆钩</v>
       </c>
       <c r="H32" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/GAMAKATSU_hooks/big_cat_circle.jpg</v>

--- a/GearSage-client/pkgGear/data_raw/gamakatsu_hook_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/gamakatsu_hook_import.xlsx
@@ -1593,7 +1593,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D2" t="str">
-        <v>Antenna Hook | 4 | 4 pack</v>
+        <v>4 | 4 pack</v>
       </c>
       <c r="E2" t="str">
         <v>特种钩</v>
@@ -1634,7 +1634,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D3" t="str">
-        <v>Antenna Hook | 2 | 4 pack</v>
+        <v>2 | 4 pack</v>
       </c>
       <c r="E3" t="str">
         <v>特种钩</v>
@@ -1675,7 +1675,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D4" t="str">
-        <v>Antenna Hook | 1 | 4 pack</v>
+        <v>1 | 4 pack</v>
       </c>
       <c r="E4" t="str">
         <v>特种钩</v>
@@ -1716,7 +1716,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D5" t="str">
-        <v>Super Tuned Drop Shot | 2 | 6 pack</v>
+        <v>2 | 6 pack</v>
       </c>
       <c r="E5" t="str">
         <v>倒钓钩</v>
@@ -1757,7 +1757,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D6" t="str">
-        <v>Super Tuned Drop Shot | 1 | 6 pack</v>
+        <v>1 | 6 pack</v>
       </c>
       <c r="E6" t="str">
         <v>倒钓钩</v>
@@ -1798,7 +1798,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D7" t="str">
-        <v>Super Tuned Drop Shot | 1/0 | 6 pack</v>
+        <v>1/0 | 6 pack</v>
       </c>
       <c r="E7" t="str">
         <v>倒钓钩</v>
@@ -1839,7 +1839,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D8" t="str">
-        <v>Super Tuned Drop Shot | 2/0 | 6 pack</v>
+        <v>2/0 | 6 pack</v>
       </c>
       <c r="E8" t="str">
         <v>倒钓钩</v>
@@ -1880,7 +1880,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D9" t="str">
-        <v>Catfish Circle Weedless | 6/0 | 4 pack</v>
+        <v>6/0 | 4 pack</v>
       </c>
       <c r="E9" t="str">
         <v>圆钩</v>
@@ -1921,7 +1921,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D10" t="str">
-        <v>Catfish Circle Weedless | 7/0 | 4 pack</v>
+        <v>7/0 | 4 pack</v>
       </c>
       <c r="E10" t="str">
         <v>圆钩</v>
@@ -1962,7 +1962,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D11" t="str">
-        <v>Catfish Circle Weedless | 8/0 | 4 pack</v>
+        <v>8/0 | 4 pack</v>
       </c>
       <c r="E11" t="str">
         <v>圆钩</v>
@@ -2003,7 +2003,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D12" t="str">
-        <v>Stiletto | 6 | 8 pack</v>
+        <v>6 | 8 pack</v>
       </c>
       <c r="E12" t="str">
         <v>特种钩</v>
@@ -2044,7 +2044,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D13" t="str">
-        <v>Stiletto | 6 | 6 pack</v>
+        <v>6 | 6 pack</v>
       </c>
       <c r="E13" t="str">
         <v>特种钩</v>
@@ -2085,7 +2085,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D14" t="str">
-        <v>Stiletto | 6 | 25 pack</v>
+        <v>6 | 25 pack</v>
       </c>
       <c r="E14" t="str">
         <v>特种钩</v>
@@ -2126,7 +2126,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D15" t="str">
-        <v>Stiletto | 4 | 8 pack</v>
+        <v>4 | 8 pack</v>
       </c>
       <c r="E15" t="str">
         <v>特种钩</v>
@@ -2167,7 +2167,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D16" t="str">
-        <v>Stiletto | 4 | 6 pack</v>
+        <v>4 | 6 pack</v>
       </c>
       <c r="E16" t="str">
         <v>特种钩</v>
@@ -2208,7 +2208,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D17" t="str">
-        <v>Stiletto | 4 | 25 pack</v>
+        <v>4 | 25 pack</v>
       </c>
       <c r="E17" t="str">
         <v>特种钩</v>
@@ -2249,7 +2249,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D18" t="str">
-        <v>Stiletto | 2 | 8 pack</v>
+        <v>2 | 8 pack</v>
       </c>
       <c r="E18" t="str">
         <v>特种钩</v>
@@ -2290,7 +2290,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D19" t="str">
-        <v>Stiletto | 2 | 6 pack</v>
+        <v>2 | 6 pack</v>
       </c>
       <c r="E19" t="str">
         <v>特种钩</v>
@@ -2331,7 +2331,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D20" t="str">
-        <v>Stiletto | 2 | 25 pack</v>
+        <v>2 | 25 pack</v>
       </c>
       <c r="E20" t="str">
         <v>特种钩</v>
@@ -2372,7 +2372,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D21" t="str">
-        <v>Stiletto | 1 | 8 pack</v>
+        <v>1 | 8 pack</v>
       </c>
       <c r="E21" t="str">
         <v>特种钩</v>
@@ -2413,7 +2413,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D22" t="str">
-        <v>Stiletto | 1 | 6 pack</v>
+        <v>1 | 6 pack</v>
       </c>
       <c r="E22" t="str">
         <v>特种钩</v>
@@ -2454,7 +2454,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D23" t="str">
-        <v>Stiletto | 1 | 25 pack</v>
+        <v>1 | 25 pack</v>
       </c>
       <c r="E23" t="str">
         <v>特种钩</v>
@@ -2495,7 +2495,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D24" t="str">
-        <v>Stiletto | 1/0 | 8 pack</v>
+        <v>1/0 | 8 pack</v>
       </c>
       <c r="E24" t="str">
         <v>特种钩</v>
@@ -2536,7 +2536,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D25" t="str">
-        <v>Stiletto | 1/0 | 6 pack</v>
+        <v>1/0 | 6 pack</v>
       </c>
       <c r="E25" t="str">
         <v>特种钩</v>
@@ -2577,7 +2577,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D26" t="str">
-        <v>Stiletto | 1/0 | 25 pack</v>
+        <v>1/0 | 25 pack</v>
       </c>
       <c r="E26" t="str">
         <v>特种钩</v>
@@ -2618,7 +2618,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D27" t="str">
-        <v>Sticker | 4 | 8 pack</v>
+        <v>4 | 8 pack</v>
       </c>
       <c r="E27" t="str">
         <v>直柄钩</v>
@@ -2659,7 +2659,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D28" t="str">
-        <v>Sticker | 4 | 6 pack</v>
+        <v>4 | 6 pack</v>
       </c>
       <c r="E28" t="str">
         <v>直柄钩</v>
@@ -2700,7 +2700,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D29" t="str">
-        <v>Sticker | 4 | 25 pack</v>
+        <v>4 | 25 pack</v>
       </c>
       <c r="E29" t="str">
         <v>直柄钩</v>
@@ -2741,7 +2741,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D30" t="str">
-        <v>Sticker | 2 | 8 pack</v>
+        <v>2 | 8 pack</v>
       </c>
       <c r="E30" t="str">
         <v>直柄钩</v>
@@ -2782,7 +2782,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D31" t="str">
-        <v>Sticker | 2 | 6 pack</v>
+        <v>2 | 6 pack</v>
       </c>
       <c r="E31" t="str">
         <v>直柄钩</v>
@@ -2823,7 +2823,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D32" t="str">
-        <v>Sticker | 2 | 25 pack</v>
+        <v>2 | 25 pack</v>
       </c>
       <c r="E32" t="str">
         <v>直柄钩</v>
@@ -2864,7 +2864,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D33" t="str">
-        <v>Sticker | 1 | 8 pack</v>
+        <v>1 | 8 pack</v>
       </c>
       <c r="E33" t="str">
         <v>直柄钩</v>
@@ -2905,7 +2905,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D34" t="str">
-        <v>Sticker | 1 | 6 pack</v>
+        <v>1 | 6 pack</v>
       </c>
       <c r="E34" t="str">
         <v>直柄钩</v>
@@ -2946,7 +2946,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D35" t="str">
-        <v>Sticker | 1 | 25 pack</v>
+        <v>1 | 25 pack</v>
       </c>
       <c r="E35" t="str">
         <v>直柄钩</v>
@@ -2987,7 +2987,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D36" t="str">
-        <v>Sticker | 1/0 | 8 pack</v>
+        <v>1/0 | 8 pack</v>
       </c>
       <c r="E36" t="str">
         <v>直柄钩</v>
@@ -3028,7 +3028,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D37" t="str">
-        <v>Sticker | 1/0 | 6 pack</v>
+        <v>1/0 | 6 pack</v>
       </c>
       <c r="E37" t="str">
         <v>直柄钩</v>
@@ -3069,7 +3069,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D38" t="str">
-        <v>Sticker | 1/0 | 25 pack</v>
+        <v>1/0 | 25 pack</v>
       </c>
       <c r="E38" t="str">
         <v>直柄钩</v>
@@ -3110,7 +3110,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D39" t="str">
-        <v>Trout Stinger | 14</v>
+        <v>14</v>
       </c>
       <c r="E39" t="str">
         <v>直柄钩</v>
@@ -3151,7 +3151,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D40" t="str">
-        <v>Trout Stinger | 12</v>
+        <v>12</v>
       </c>
       <c r="E40" t="str">
         <v>直柄钩</v>
@@ -3192,7 +3192,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D41" t="str">
-        <v>Trout Stinger | 10</v>
+        <v>10</v>
       </c>
       <c r="E41" t="str">
         <v>直柄钩</v>
@@ -3233,7 +3233,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D42" t="str">
-        <v>Trout Stinger | 8</v>
+        <v>8</v>
       </c>
       <c r="E42" t="str">
         <v>直柄钩</v>
@@ -3274,7 +3274,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D43" t="str">
-        <v>Spin Bait | 4 | 4 pack</v>
+        <v>4 | 4 pack</v>
       </c>
       <c r="E43" t="str">
         <v>挂钩</v>
@@ -3315,7 +3315,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D44" t="str">
-        <v>Spin Bait | 2 | 4 pack</v>
+        <v>2 | 4 pack</v>
       </c>
       <c r="E44" t="str">
         <v>挂钩</v>
@@ -3356,7 +3356,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D45" t="str">
-        <v>Spin Bait | 1 | 4 pack</v>
+        <v>1 | 4 pack</v>
       </c>
       <c r="E45" t="str">
         <v>挂钩</v>
@@ -3397,7 +3397,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D46" t="str">
-        <v>Spin Bait | 1/0 | 4 pack</v>
+        <v>1/0 | 4 pack</v>
       </c>
       <c r="E46" t="str">
         <v>挂钩</v>
@@ -3438,7 +3438,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D47" t="str">
-        <v>Aberdeen | 8 | 10 pack</v>
+        <v>8 | 10 pack</v>
       </c>
       <c r="E47" t="str">
         <v>直柄钩</v>
@@ -3479,7 +3479,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D48" t="str">
-        <v>Aberdeen | 8 | 8 pack</v>
+        <v>8 | 8 pack</v>
       </c>
       <c r="E48" t="str">
         <v>直柄钩</v>
@@ -3520,7 +3520,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D49" t="str">
-        <v>Aberdeen | 8 | 6 pack</v>
+        <v>8 | 6 pack</v>
       </c>
       <c r="E49" t="str">
         <v>直柄钩</v>
@@ -3561,7 +3561,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D50" t="str">
-        <v>Aberdeen | 6 | 10 pack</v>
+        <v>6 | 10 pack</v>
       </c>
       <c r="E50" t="str">
         <v>直柄钩</v>
@@ -3602,7 +3602,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D51" t="str">
-        <v>Aberdeen | 6 | 8 pack</v>
+        <v>6 | 8 pack</v>
       </c>
       <c r="E51" t="str">
         <v>直柄钩</v>
@@ -3643,7 +3643,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D52" t="str">
-        <v>Aberdeen | 6 | 6 pack</v>
+        <v>6 | 6 pack</v>
       </c>
       <c r="E52" t="str">
         <v>直柄钩</v>
@@ -3684,7 +3684,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D53" t="str">
-        <v>Aberdeen | 4 | 10 pack</v>
+        <v>4 | 10 pack</v>
       </c>
       <c r="E53" t="str">
         <v>直柄钩</v>
@@ -3725,7 +3725,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D54" t="str">
-        <v>Aberdeen | 4 | 8 pack</v>
+        <v>4 | 8 pack</v>
       </c>
       <c r="E54" t="str">
         <v>直柄钩</v>
@@ -3766,7 +3766,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D55" t="str">
-        <v>Aberdeen | 4 | 6 pack</v>
+        <v>4 | 6 pack</v>
       </c>
       <c r="E55" t="str">
         <v>直柄钩</v>
@@ -3807,7 +3807,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D56" t="str">
-        <v>Aberdeen | 2 | 10 pack</v>
+        <v>2 | 10 pack</v>
       </c>
       <c r="E56" t="str">
         <v>直柄钩</v>
@@ -3848,7 +3848,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D57" t="str">
-        <v>Aberdeen | 2 | 8 pack</v>
+        <v>2 | 8 pack</v>
       </c>
       <c r="E57" t="str">
         <v>直柄钩</v>
@@ -3889,7 +3889,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D58" t="str">
-        <v>Aberdeen | 2 | 6 pack</v>
+        <v>2 | 6 pack</v>
       </c>
       <c r="E58" t="str">
         <v>直柄钩</v>
@@ -3930,7 +3930,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D59" t="str">
-        <v>Aberdeen | 1 | 10 pack</v>
+        <v>1 | 10 pack</v>
       </c>
       <c r="E59" t="str">
         <v>直柄钩</v>
@@ -3971,7 +3971,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D60" t="str">
-        <v>Aberdeen | 1 | 8 pack</v>
+        <v>1 | 8 pack</v>
       </c>
       <c r="E60" t="str">
         <v>直柄钩</v>
@@ -4012,7 +4012,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D61" t="str">
-        <v>Aberdeen | 1 | 6 pack</v>
+        <v>1 | 6 pack</v>
       </c>
       <c r="E61" t="str">
         <v>直柄钩</v>
@@ -4053,7 +4053,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D62" t="str">
-        <v>Wicked Wacky | 1/0 | 3 pack</v>
+        <v>1/0 | 3 pack</v>
       </c>
       <c r="E62" t="str">
         <v>倒钓钩</v>
@@ -4094,7 +4094,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D63" t="str">
-        <v>Wicked Wacky | 2/0 | 3 pack</v>
+        <v>2/0 | 3 pack</v>
       </c>
       <c r="E63" t="str">
         <v>倒钓钩</v>
@@ -4135,7 +4135,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D64" t="str">
-        <v>Wicked Wacky | 3/0 | 3 pack</v>
+        <v>3/0 | 3 pack</v>
       </c>
       <c r="E64" t="str">
         <v>倒钓钩</v>
@@ -4176,7 +4176,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D65" t="str">
-        <v>Wicked Wacky | 4/0 | 3 pack</v>
+        <v>4/0 | 3 pack</v>
       </c>
       <c r="E65" t="str">
         <v>倒钓钩</v>
@@ -4217,7 +4217,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D66" t="str">
-        <v>Wicked Wacky | 5/0 | 3 pack</v>
+        <v>5/0 | 3 pack</v>
       </c>
       <c r="E66" t="str">
         <v>倒钓钩</v>
@@ -4258,7 +4258,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D67" t="str">
-        <v>Walleye Wide Gap | 8 | 10 pack</v>
+        <v>8 | 10 pack</v>
       </c>
       <c r="E67" t="str">
         <v>曲柄钩</v>
@@ -4299,7 +4299,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D68" t="str">
-        <v>Walleye Wide Gap | 8 | 25 pack</v>
+        <v>8 | 25 pack</v>
       </c>
       <c r="E68" t="str">
         <v>曲柄钩</v>
@@ -4340,7 +4340,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D69" t="str">
-        <v>Walleye Wide Gap | 8 | 6 pack</v>
+        <v>8 | 6 pack</v>
       </c>
       <c r="E69" t="str">
         <v>曲柄钩</v>
@@ -4381,7 +4381,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D70" t="str">
-        <v>Walleye Wide Gap | 8 | 8 pack</v>
+        <v>8 | 8 pack</v>
       </c>
       <c r="E70" t="str">
         <v>曲柄钩</v>
@@ -4422,7 +4422,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D71" t="str">
-        <v>Walleye Wide Gap | 6 | 10 pack</v>
+        <v>6 | 10 pack</v>
       </c>
       <c r="E71" t="str">
         <v>曲柄钩</v>
@@ -4463,7 +4463,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D72" t="str">
-        <v>Walleye Wide Gap | 6 | 25 pack</v>
+        <v>6 | 25 pack</v>
       </c>
       <c r="E72" t="str">
         <v>曲柄钩</v>
@@ -4504,7 +4504,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D73" t="str">
-        <v>Walleye Wide Gap | 6 | 6 pack</v>
+        <v>6 | 6 pack</v>
       </c>
       <c r="E73" t="str">
         <v>曲柄钩</v>
@@ -4545,7 +4545,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D74" t="str">
-        <v>Walleye Wide Gap | 6 | 8 pack</v>
+        <v>6 | 8 pack</v>
       </c>
       <c r="E74" t="str">
         <v>曲柄钩</v>
@@ -4586,7 +4586,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D75" t="str">
-        <v>Walleye Wide Gap | 4 | 10 pack</v>
+        <v>4 | 10 pack</v>
       </c>
       <c r="E75" t="str">
         <v>曲柄钩</v>
@@ -4627,7 +4627,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D76" t="str">
-        <v>Walleye Wide Gap | 4 | 25 pack</v>
+        <v>4 | 25 pack</v>
       </c>
       <c r="E76" t="str">
         <v>曲柄钩</v>
@@ -4668,7 +4668,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D77" t="str">
-        <v>Walleye Wide Gap | 4 | 6 pack</v>
+        <v>4 | 6 pack</v>
       </c>
       <c r="E77" t="str">
         <v>曲柄钩</v>
@@ -4709,7 +4709,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D78" t="str">
-        <v>Walleye Wide Gap | 4 | 8 pack</v>
+        <v>4 | 8 pack</v>
       </c>
       <c r="E78" t="str">
         <v>曲柄钩</v>
@@ -4750,7 +4750,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D79" t="str">
-        <v>Walleye Wide Gap | 2 | 10 pack</v>
+        <v>2 | 10 pack</v>
       </c>
       <c r="E79" t="str">
         <v>曲柄钩</v>
@@ -4791,7 +4791,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D80" t="str">
-        <v>Walleye Wide Gap | 2 | 25 pack</v>
+        <v>2 | 25 pack</v>
       </c>
       <c r="E80" t="str">
         <v>曲柄钩</v>
@@ -4832,7 +4832,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D81" t="str">
-        <v>Walleye Wide Gap | 2 | 6 pack</v>
+        <v>2 | 6 pack</v>
       </c>
       <c r="E81" t="str">
         <v>曲柄钩</v>
@@ -4873,7 +4873,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D82" t="str">
-        <v>Walleye Wide Gap | 2 | 8 pack</v>
+        <v>2 | 8 pack</v>
       </c>
       <c r="E82" t="str">
         <v>曲柄钩</v>
@@ -4914,7 +4914,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D83" t="str">
-        <v>Walleye Wide Gap | 1 | 10 pack</v>
+        <v>1 | 10 pack</v>
       </c>
       <c r="E83" t="str">
         <v>曲柄钩</v>
@@ -4955,7 +4955,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D84" t="str">
-        <v>Walleye Wide Gap | 1 | 25 pack</v>
+        <v>1 | 25 pack</v>
       </c>
       <c r="E84" t="str">
         <v>曲柄钩</v>
@@ -4996,7 +4996,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D85" t="str">
-        <v>Walleye Wide Gap | 1 | 6 pack</v>
+        <v>1 | 6 pack</v>
       </c>
       <c r="E85" t="str">
         <v>曲柄钩</v>
@@ -5037,7 +5037,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D86" t="str">
-        <v>Walleye Wide Gap | 1 | 8 pack</v>
+        <v>1 | 8 pack</v>
       </c>
       <c r="E86" t="str">
         <v>曲柄钩</v>
@@ -5078,7 +5078,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D87" t="str">
-        <v>Walleye Wide Gap | 1/0 | 10 pack</v>
+        <v>1/0 | 10 pack</v>
       </c>
       <c r="E87" t="str">
         <v>曲柄钩</v>
@@ -5119,7 +5119,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D88" t="str">
-        <v>Walleye Wide Gap | 1/0 | 25 pack</v>
+        <v>1/0 | 25 pack</v>
       </c>
       <c r="E88" t="str">
         <v>曲柄钩</v>
@@ -5160,7 +5160,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D89" t="str">
-        <v>Walleye Wide Gap | 1/0 | 6 pack</v>
+        <v>1/0 | 6 pack</v>
       </c>
       <c r="E89" t="str">
         <v>曲柄钩</v>
@@ -5201,7 +5201,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D90" t="str">
-        <v>Walleye Wide Gap | 1/0 | 8 pack</v>
+        <v>1/0 | 8 pack</v>
       </c>
       <c r="E90" t="str">
         <v>曲柄钩</v>
@@ -5242,7 +5242,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D91" t="str">
-        <v>Walleye Wide Gap | 2/0 | 10 pack</v>
+        <v>2/0 | 10 pack</v>
       </c>
       <c r="E91" t="str">
         <v>曲柄钩</v>
@@ -5283,7 +5283,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D92" t="str">
-        <v>Walleye Wide Gap | 2/0 | 25 pack</v>
+        <v>2/0 | 25 pack</v>
       </c>
       <c r="E92" t="str">
         <v>曲柄钩</v>
@@ -5324,7 +5324,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D93" t="str">
-        <v>Walleye Wide Gap | 2/0 | 6 pack</v>
+        <v>2/0 | 6 pack</v>
       </c>
       <c r="E93" t="str">
         <v>曲柄钩</v>
@@ -5365,7 +5365,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D94" t="str">
-        <v>Walleye Wide Gap | 2/0 | 8 pack</v>
+        <v>2/0 | 8 pack</v>
       </c>
       <c r="E94" t="str">
         <v>曲柄钩</v>
@@ -5406,7 +5406,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D95" t="str">
-        <v>TW Hook | 16 | 10 pack</v>
+        <v>16 | 10 pack</v>
       </c>
       <c r="E95" t="str">
         <v>直柄钩</v>
@@ -5447,7 +5447,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D96" t="str">
-        <v>TW Hook | 14 | 10 pack</v>
+        <v>14 | 10 pack</v>
       </c>
       <c r="E96" t="str">
         <v>直柄钩</v>
@@ -5488,7 +5488,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D97" t="str">
-        <v>TW Hook | 12 | 10 pack</v>
+        <v>12 | 10 pack</v>
       </c>
       <c r="E97" t="str">
         <v>直柄钩</v>
@@ -5529,7 +5529,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D98" t="str">
-        <v>TW Hook | 10 | 10 pack</v>
+        <v>10 | 10 pack</v>
       </c>
       <c r="E98" t="str">
         <v>直柄钩</v>
@@ -5570,7 +5570,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D99" t="str">
-        <v>TW Hook | 8 | 10 pack</v>
+        <v>8 | 10 pack</v>
       </c>
       <c r="E99" t="str">
         <v>直柄钩</v>
@@ -5611,7 +5611,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D100" t="str">
-        <v>TW Hook | 6 | 10 pack</v>
+        <v>6 | 10 pack</v>
       </c>
       <c r="E100" t="str">
         <v>直柄钩</v>
@@ -5652,7 +5652,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D101" t="str">
-        <v>Trailer Hook SP | 1 | 4 pack</v>
+        <v>1 | 4 pack</v>
       </c>
       <c r="E101" t="str">
         <v>挂钩</v>
@@ -5693,7 +5693,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D102" t="str">
-        <v>Trailer Hook SP | 1 | 5 pack</v>
+        <v>1 | 5 pack</v>
       </c>
       <c r="E102" t="str">
         <v>挂钩</v>
@@ -5734,7 +5734,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D103" t="str">
-        <v>Trailer Hook SP | 1/0 | 4 pack</v>
+        <v>1/0 | 4 pack</v>
       </c>
       <c r="E103" t="str">
         <v>挂钩</v>
@@ -5775,7 +5775,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D104" t="str">
-        <v>Trailer Hook SP | 1/0 | 5 pack</v>
+        <v>1/0 | 5 pack</v>
       </c>
       <c r="E104" t="str">
         <v>挂钩</v>
@@ -5816,7 +5816,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D105" t="str">
-        <v>Trailer Hook SP | 2/0 | 4 pack</v>
+        <v>2/0 | 4 pack</v>
       </c>
       <c r="E105" t="str">
         <v>挂钩</v>
@@ -5857,7 +5857,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D106" t="str">
-        <v>Trailer Hook SP | 2/0 | 5 pack</v>
+        <v>2/0 | 5 pack</v>
       </c>
       <c r="E106" t="str">
         <v>挂钩</v>
@@ -5898,7 +5898,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D107" t="str">
-        <v>Trailer Hook SP | 3/0 | 4 pack</v>
+        <v>3/0 | 4 pack</v>
       </c>
       <c r="E107" t="str">
         <v>挂钩</v>
@@ -5939,7 +5939,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D108" t="str">
-        <v>Trailer Hook SP | 3/0 | 5 pack</v>
+        <v>3/0 | 5 pack</v>
       </c>
       <c r="E108" t="str">
         <v>挂钩</v>
@@ -5980,7 +5980,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D109" t="str">
-        <v>Split Shot/Drop Shot Weedless | 4 | 4 pack</v>
+        <v>4 | 4 pack</v>
       </c>
       <c r="E109" t="str">
         <v>倒钓钩</v>
@@ -6021,7 +6021,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D110" t="str">
-        <v>Split Shot/Drop Shot Weedless | 4 | 5 pack</v>
+        <v>4 | 5 pack</v>
       </c>
       <c r="E110" t="str">
         <v>倒钓钩</v>
@@ -6062,7 +6062,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D111" t="str">
-        <v>Split Shot/Drop Shot Weedless | 2 | 4 pack</v>
+        <v>2 | 4 pack</v>
       </c>
       <c r="E111" t="str">
         <v>倒钓钩</v>
@@ -6103,7 +6103,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D112" t="str">
-        <v>Split Shot/Drop Shot Weedless | 2 | 5 pack</v>
+        <v>2 | 5 pack</v>
       </c>
       <c r="E112" t="str">
         <v>倒钓钩</v>
@@ -6144,7 +6144,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D113" t="str">
-        <v>Split Shot/Drop Shot Weedless | 1 | 4 pack</v>
+        <v>1 | 4 pack</v>
       </c>
       <c r="E113" t="str">
         <v>倒钓钩</v>
@@ -6185,7 +6185,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D114" t="str">
-        <v>Split Shot/Drop Shot Weedless | 1 | 5 pack</v>
+        <v>1 | 5 pack</v>
       </c>
       <c r="E114" t="str">
         <v>倒钓钩</v>
@@ -6226,7 +6226,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D115" t="str">
-        <v>Split Shot/Drop Shot Weedless | 1/0 | 4 pack</v>
+        <v>1/0 | 4 pack</v>
       </c>
       <c r="E115" t="str">
         <v>倒钓钩</v>
@@ -6267,7 +6267,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D116" t="str">
-        <v>Split Shot/Drop Shot Weedless | 1/0 | 5 pack</v>
+        <v>1/0 | 5 pack</v>
       </c>
       <c r="E116" t="str">
         <v>倒钓钩</v>
@@ -6308,7 +6308,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D117" t="str">
-        <v>Split Shot/Drop Shot Weedless | 2/0 | 4 pack</v>
+        <v>2/0 | 4 pack</v>
       </c>
       <c r="E117" t="str">
         <v>倒钓钩</v>
@@ -6349,7 +6349,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D118" t="str">
-        <v>Split Shot/Drop Shot Weedless | 2/0 | 5 pack</v>
+        <v>2/0 | 5 pack</v>
       </c>
       <c r="E118" t="str">
         <v>倒钓钩</v>
@@ -6390,7 +6390,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D119" t="str">
-        <v>Split Shot/Drop Shot Weedless | 3/0 | 4 pack</v>
+        <v>3/0 | 4 pack</v>
       </c>
       <c r="E119" t="str">
         <v>倒钓钩</v>
@@ -6431,7 +6431,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D120" t="str">
-        <v>Split Shot/Drop Shot Weedless | 3/0 | 5 pack</v>
+        <v>3/0 | 5 pack</v>
       </c>
       <c r="E120" t="str">
         <v>倒钓钩</v>
@@ -6472,7 +6472,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D121" t="str">
-        <v>Split Shot/Drop Shot | 4 | 25 pack</v>
+        <v>4 | 25 pack</v>
       </c>
       <c r="E121" t="str">
         <v>倒钓钩</v>
@@ -6513,7 +6513,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D122" t="str">
-        <v>Split Shot/Drop Shot | 4 | 6 pack</v>
+        <v>4 | 6 pack</v>
       </c>
       <c r="E122" t="str">
         <v>倒钓钩</v>
@@ -6554,7 +6554,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D123" t="str">
-        <v>Split Shot/Drop Shot | 2 | 25 pack</v>
+        <v>2 | 25 pack</v>
       </c>
       <c r="E123" t="str">
         <v>倒钓钩</v>
@@ -6595,7 +6595,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D124" t="str">
-        <v>Split Shot/Drop Shot | 2 | 6 pack</v>
+        <v>2 | 6 pack</v>
       </c>
       <c r="E124" t="str">
         <v>倒钓钩</v>
@@ -6636,7 +6636,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D125" t="str">
-        <v>Split Shot/Drop Shot | 1 | 25 pack</v>
+        <v>1 | 25 pack</v>
       </c>
       <c r="E125" t="str">
         <v>倒钓钩</v>
@@ -6677,7 +6677,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D126" t="str">
-        <v>Split Shot/Drop Shot | 1 | 6 pack</v>
+        <v>1 | 6 pack</v>
       </c>
       <c r="E126" t="str">
         <v>倒钓钩</v>
@@ -6718,7 +6718,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D127" t="str">
-        <v>Split Shot/Drop Shot | 1/0 | 25 pack</v>
+        <v>1/0 | 25 pack</v>
       </c>
       <c r="E127" t="str">
         <v>倒钓钩</v>
@@ -6759,7 +6759,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D128" t="str">
-        <v>Split Shot/Drop Shot | 1/0 | 6 pack</v>
+        <v>1/0 | 6 pack</v>
       </c>
       <c r="E128" t="str">
         <v>倒钓钩</v>
@@ -6800,7 +6800,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D129" t="str">
-        <v>Split Shot/Drop Shot | 2/0 | 25 pack</v>
+        <v>2/0 | 25 pack</v>
       </c>
       <c r="E129" t="str">
         <v>倒钓钩</v>
@@ -6841,7 +6841,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D130" t="str">
-        <v>Split Shot/Drop Shot | 2/0 | 6 pack</v>
+        <v>2/0 | 6 pack</v>
       </c>
       <c r="E130" t="str">
         <v>倒钓钩</v>
@@ -6882,7 +6882,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D131" t="str">
-        <v>Split Shot/Drop Shot | 3/0 | 25 pack</v>
+        <v>3/0 | 25 pack</v>
       </c>
       <c r="E131" t="str">
         <v>倒钓钩</v>
@@ -6923,7 +6923,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D132" t="str">
-        <v>Split Shot/Drop Shot | 3/0 | 6 pack</v>
+        <v>3/0 | 6 pack</v>
       </c>
       <c r="E132" t="str">
         <v>倒钓钩</v>
@@ -6964,7 +6964,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D133" t="str">
-        <v>Spinner Bait | 1/0 | 100 pack</v>
+        <v>1/0 | 100 pack</v>
       </c>
       <c r="E133" t="str">
         <v>挂钩</v>
@@ -7005,7 +7005,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D134" t="str">
-        <v>Spinner Bait | 1/0 | 25 pack</v>
+        <v>1/0 | 25 pack</v>
       </c>
       <c r="E134" t="str">
         <v>挂钩</v>
@@ -7046,7 +7046,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D135" t="str">
-        <v>Spinner Bait | 2/0 | 100 pack</v>
+        <v>2/0 | 100 pack</v>
       </c>
       <c r="E135" t="str">
         <v>挂钩</v>
@@ -7087,7 +7087,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D136" t="str">
-        <v>Spinner Bait | 2/0 | 25 pack</v>
+        <v>2/0 | 25 pack</v>
       </c>
       <c r="E136" t="str">
         <v>挂钩</v>
@@ -7128,7 +7128,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D137" t="str">
-        <v>Spinner Bait | 3/0 | 100 pack</v>
+        <v>3/0 | 100 pack</v>
       </c>
       <c r="E137" t="str">
         <v>挂钩</v>
@@ -7169,7 +7169,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D138" t="str">
-        <v>Spinner Bait | 3/0 | 25 pack</v>
+        <v>3/0 | 25 pack</v>
       </c>
       <c r="E138" t="str">
         <v>挂钩</v>
@@ -7210,7 +7210,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D139" t="str">
-        <v>Spinner Bait | 4/0 | 100 pack</v>
+        <v>4/0 | 100 pack</v>
       </c>
       <c r="E139" t="str">
         <v>挂钩</v>
@@ -7251,7 +7251,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D140" t="str">
-        <v>Spinner Bait | 4/0 | 25 pack</v>
+        <v>4/0 | 25 pack</v>
       </c>
       <c r="E140" t="str">
         <v>挂钩</v>
@@ -7292,7 +7292,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D141" t="str">
-        <v>Spinner Bait | 5/0 | 100 pack</v>
+        <v>5/0 | 100 pack</v>
       </c>
       <c r="E141" t="str">
         <v>挂钩</v>
@@ -7333,7 +7333,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D142" t="str">
-        <v>Spinner Bait | 5/0 | 25 pack</v>
+        <v>5/0 | 25 pack</v>
       </c>
       <c r="E142" t="str">
         <v>挂钩</v>
@@ -7374,7 +7374,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D143" t="str">
-        <v>Single Egg Hook, Barb on Shank | 14 | 10 pack</v>
+        <v>14 | 10 pack</v>
       </c>
       <c r="E143" t="str">
         <v>直柄钩</v>
@@ -7415,7 +7415,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D144" t="str">
-        <v>Single Egg Hook, Barb on Shank | 12 | 10 pack</v>
+        <v>12 | 10 pack</v>
       </c>
       <c r="E144" t="str">
         <v>直柄钩</v>
@@ -7456,7 +7456,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D145" t="str">
-        <v>Single Egg Hook, Barb on Shank | 10 | 10 pack</v>
+        <v>10 | 10 pack</v>
       </c>
       <c r="E145" t="str">
         <v>直柄钩</v>
@@ -7497,7 +7497,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D146" t="str">
-        <v>Single Egg Hook, Barb on Shank | 8 | 10 pack</v>
+        <v>8 | 10 pack</v>
       </c>
       <c r="E146" t="str">
         <v>直柄钩</v>
@@ -7538,7 +7538,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D147" t="str">
-        <v>Single Egg Hook, Barb on Shank | 6 | 10 pack</v>
+        <v>6 | 10 pack</v>
       </c>
       <c r="E147" t="str">
         <v>直柄钩</v>
@@ -7579,7 +7579,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D148" t="str">
-        <v>Shiner Upturned Eye | 6 | 25 pack</v>
+        <v>6 | 25 pack</v>
       </c>
       <c r="E148" t="str">
         <v>直柄钩</v>
@@ -7620,7 +7620,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D149" t="str">
-        <v>Shiner Upturned Eye | 6 | 3 pack</v>
+        <v>6 | 3 pack</v>
       </c>
       <c r="E149" t="str">
         <v>直柄钩</v>
@@ -7661,7 +7661,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D150" t="str">
-        <v>Shiner Upturned Eye | 6 | 4 pack</v>
+        <v>6 | 4 pack</v>
       </c>
       <c r="E150" t="str">
         <v>直柄钩</v>
@@ -7702,7 +7702,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D151" t="str">
-        <v>Shiner Upturned Eye | 6 | 5 pack</v>
+        <v>6 | 5 pack</v>
       </c>
       <c r="E151" t="str">
         <v>直柄钩</v>
@@ -7743,7 +7743,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D152" t="str">
-        <v>Shiner Upturned Eye | 6 | 6 pack</v>
+        <v>6 | 6 pack</v>
       </c>
       <c r="E152" t="str">
         <v>直柄钩</v>
@@ -7784,7 +7784,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D153" t="str">
-        <v>Shiner Upturned Eye | 6 | 7 pack</v>
+        <v>6 | 7 pack</v>
       </c>
       <c r="E153" t="str">
         <v>直柄钩</v>
@@ -7825,7 +7825,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D154" t="str">
-        <v>Shiner Upturned Eye | 6 | 8 pack</v>
+        <v>6 | 8 pack</v>
       </c>
       <c r="E154" t="str">
         <v>直柄钩</v>
@@ -7866,7 +7866,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D155" t="str">
-        <v>Shiner Upturned Eye | 4 | 25 pack</v>
+        <v>4 | 25 pack</v>
       </c>
       <c r="E155" t="str">
         <v>直柄钩</v>
@@ -7907,7 +7907,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D156" t="str">
-        <v>Shiner Upturned Eye | 4 | 3 pack</v>
+        <v>4 | 3 pack</v>
       </c>
       <c r="E156" t="str">
         <v>直柄钩</v>
@@ -7948,7 +7948,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D157" t="str">
-        <v>Shiner Upturned Eye | 4 | 4 pack</v>
+        <v>4 | 4 pack</v>
       </c>
       <c r="E157" t="str">
         <v>直柄钩</v>
@@ -7989,7 +7989,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D158" t="str">
-        <v>Shiner Upturned Eye | 4 | 5 pack</v>
+        <v>4 | 5 pack</v>
       </c>
       <c r="E158" t="str">
         <v>直柄钩</v>
@@ -8030,7 +8030,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D159" t="str">
-        <v>Shiner Upturned Eye | 4 | 6 pack</v>
+        <v>4 | 6 pack</v>
       </c>
       <c r="E159" t="str">
         <v>直柄钩</v>
@@ -8071,7 +8071,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D160" t="str">
-        <v>Shiner Upturned Eye | 4 | 7 pack</v>
+        <v>4 | 7 pack</v>
       </c>
       <c r="E160" t="str">
         <v>直柄钩</v>
@@ -8112,7 +8112,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D161" t="str">
-        <v>Shiner Upturned Eye | 4 | 8 pack</v>
+        <v>4 | 8 pack</v>
       </c>
       <c r="E161" t="str">
         <v>直柄钩</v>
@@ -8153,7 +8153,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D162" t="str">
-        <v>Shiner Upturned Eye | 2 | 25 pack</v>
+        <v>2 | 25 pack</v>
       </c>
       <c r="E162" t="str">
         <v>直柄钩</v>
@@ -8194,7 +8194,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D163" t="str">
-        <v>Shiner Upturned Eye | 2 | 3 pack</v>
+        <v>2 | 3 pack</v>
       </c>
       <c r="E163" t="str">
         <v>直柄钩</v>
@@ -8235,7 +8235,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D164" t="str">
-        <v>Shiner Upturned Eye | 2 | 4 pack</v>
+        <v>2 | 4 pack</v>
       </c>
       <c r="E164" t="str">
         <v>直柄钩</v>
@@ -8276,7 +8276,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D165" t="str">
-        <v>Shiner Upturned Eye | 2 | 5 pack</v>
+        <v>2 | 5 pack</v>
       </c>
       <c r="E165" t="str">
         <v>直柄钩</v>
@@ -8317,7 +8317,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D166" t="str">
-        <v>Shiner Upturned Eye | 2 | 6 pack</v>
+        <v>2 | 6 pack</v>
       </c>
       <c r="E166" t="str">
         <v>直柄钩</v>
@@ -8358,7 +8358,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D167" t="str">
-        <v>Shiner Upturned Eye | 2 | 7 pack</v>
+        <v>2 | 7 pack</v>
       </c>
       <c r="E167" t="str">
         <v>直柄钩</v>
@@ -8399,7 +8399,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D168" t="str">
-        <v>Shiner Upturned Eye | 2 | 8 pack</v>
+        <v>2 | 8 pack</v>
       </c>
       <c r="E168" t="str">
         <v>直柄钩</v>
@@ -8440,7 +8440,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D169" t="str">
-        <v>Shiner Upturned Eye | 1 | 25 pack</v>
+        <v>1 | 25 pack</v>
       </c>
       <c r="E169" t="str">
         <v>直柄钩</v>
@@ -8481,7 +8481,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D170" t="str">
-        <v>Shiner Upturned Eye | 1 | 3 pack</v>
+        <v>1 | 3 pack</v>
       </c>
       <c r="E170" t="str">
         <v>直柄钩</v>
@@ -8522,7 +8522,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D171" t="str">
-        <v>Shiner Upturned Eye | 1 | 4 pack</v>
+        <v>1 | 4 pack</v>
       </c>
       <c r="E171" t="str">
         <v>直柄钩</v>
@@ -8563,7 +8563,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D172" t="str">
-        <v>Shiner Upturned Eye | 1 | 5 pack</v>
+        <v>1 | 5 pack</v>
       </c>
       <c r="E172" t="str">
         <v>直柄钩</v>
@@ -8604,7 +8604,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D173" t="str">
-        <v>Shiner Upturned Eye | 1 | 6 pack</v>
+        <v>1 | 6 pack</v>
       </c>
       <c r="E173" t="str">
         <v>直柄钩</v>
@@ -8645,7 +8645,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D174" t="str">
-        <v>Shiner Upturned Eye | 1 | 7 pack</v>
+        <v>1 | 7 pack</v>
       </c>
       <c r="E174" t="str">
         <v>直柄钩</v>
@@ -8686,7 +8686,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D175" t="str">
-        <v>Shiner Upturned Eye | 1 | 8 pack</v>
+        <v>1 | 8 pack</v>
       </c>
       <c r="E175" t="str">
         <v>直柄钩</v>
@@ -8727,7 +8727,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D176" t="str">
-        <v>Shiner Upturned Eye | 1/0 | 25 pack</v>
+        <v>1/0 | 25 pack</v>
       </c>
       <c r="E176" t="str">
         <v>直柄钩</v>
@@ -8768,7 +8768,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D177" t="str">
-        <v>Shiner Upturned Eye | 1/0 | 3 pack</v>
+        <v>1/0 | 3 pack</v>
       </c>
       <c r="E177" t="str">
         <v>直柄钩</v>
@@ -8809,7 +8809,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D178" t="str">
-        <v>Shiner Upturned Eye | 1/0 | 4 pack</v>
+        <v>1/0 | 4 pack</v>
       </c>
       <c r="E178" t="str">
         <v>直柄钩</v>
@@ -8850,7 +8850,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D179" t="str">
-        <v>Shiner Upturned Eye | 1/0 | 5 pack</v>
+        <v>1/0 | 5 pack</v>
       </c>
       <c r="E179" t="str">
         <v>直柄钩</v>
@@ -8891,7 +8891,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D180" t="str">
-        <v>Shiner Upturned Eye | 1/0 | 6 pack</v>
+        <v>1/0 | 6 pack</v>
       </c>
       <c r="E180" t="str">
         <v>直柄钩</v>
@@ -8932,7 +8932,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D181" t="str">
-        <v>Shiner Upturned Eye | 1/0 | 7 pack</v>
+        <v>1/0 | 7 pack</v>
       </c>
       <c r="E181" t="str">
         <v>直柄钩</v>
@@ -8973,7 +8973,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D182" t="str">
-        <v>Shiner Upturned Eye | 1/0 | 8 pack</v>
+        <v>1/0 | 8 pack</v>
       </c>
       <c r="E182" t="str">
         <v>直柄钩</v>
@@ -9014,7 +9014,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D183" t="str">
-        <v>Shiner Upturned Eye | 2/0 | 25 pack</v>
+        <v>2/0 | 25 pack</v>
       </c>
       <c r="E183" t="str">
         <v>直柄钩</v>
@@ -9055,7 +9055,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D184" t="str">
-        <v>Shiner Upturned Eye | 2/0 | 3 pack</v>
+        <v>2/0 | 3 pack</v>
       </c>
       <c r="E184" t="str">
         <v>直柄钩</v>
@@ -9096,7 +9096,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D185" t="str">
-        <v>Shiner Upturned Eye | 2/0 | 4 pack</v>
+        <v>2/0 | 4 pack</v>
       </c>
       <c r="E185" t="str">
         <v>直柄钩</v>
@@ -9137,7 +9137,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D186" t="str">
-        <v>Shiner Upturned Eye | 2/0 | 5 pack</v>
+        <v>2/0 | 5 pack</v>
       </c>
       <c r="E186" t="str">
         <v>直柄钩</v>
@@ -9178,7 +9178,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D187" t="str">
-        <v>Shiner Upturned Eye | 2/0 | 6 pack</v>
+        <v>2/0 | 6 pack</v>
       </c>
       <c r="E187" t="str">
         <v>直柄钩</v>
@@ -9219,7 +9219,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D188" t="str">
-        <v>Shiner Upturned Eye | 2/0 | 7 pack</v>
+        <v>2/0 | 7 pack</v>
       </c>
       <c r="E188" t="str">
         <v>直柄钩</v>
@@ -9260,7 +9260,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D189" t="str">
-        <v>Shiner Upturned Eye | 2/0 | 8 pack</v>
+        <v>2/0 | 8 pack</v>
       </c>
       <c r="E189" t="str">
         <v>直柄钩</v>
@@ -9301,7 +9301,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D190" t="str">
-        <v>Shiner Upturned Eye | 3/0 | 25 pack</v>
+        <v>3/0 | 25 pack</v>
       </c>
       <c r="E190" t="str">
         <v>直柄钩</v>
@@ -9342,7 +9342,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D191" t="str">
-        <v>Shiner Upturned Eye | 3/0 | 3 pack</v>
+        <v>3/0 | 3 pack</v>
       </c>
       <c r="E191" t="str">
         <v>直柄钩</v>
@@ -9383,7 +9383,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D192" t="str">
-        <v>Shiner Upturned Eye | 3/0 | 4 pack</v>
+        <v>3/0 | 4 pack</v>
       </c>
       <c r="E192" t="str">
         <v>直柄钩</v>
@@ -9424,7 +9424,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D193" t="str">
-        <v>Shiner Upturned Eye | 3/0 | 5 pack</v>
+        <v>3/0 | 5 pack</v>
       </c>
       <c r="E193" t="str">
         <v>直柄钩</v>
@@ -9465,7 +9465,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D194" t="str">
-        <v>Shiner Upturned Eye | 3/0 | 6 pack</v>
+        <v>3/0 | 6 pack</v>
       </c>
       <c r="E194" t="str">
         <v>直柄钩</v>
@@ -9506,7 +9506,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D195" t="str">
-        <v>Shiner Upturned Eye | 3/0 | 7 pack</v>
+        <v>3/0 | 7 pack</v>
       </c>
       <c r="E195" t="str">
         <v>直柄钩</v>
@@ -9547,7 +9547,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D196" t="str">
-        <v>Shiner Upturned Eye | 3/0 | 8 pack</v>
+        <v>3/0 | 8 pack</v>
       </c>
       <c r="E196" t="str">
         <v>直柄钩</v>
@@ -9588,7 +9588,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D197" t="str">
-        <v>Shiner Upturned Eye | 4/0 | 25 pack</v>
+        <v>4/0 | 25 pack</v>
       </c>
       <c r="E197" t="str">
         <v>直柄钩</v>
@@ -9629,7 +9629,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D198" t="str">
-        <v>Shiner Upturned Eye | 4/0 | 3 pack</v>
+        <v>4/0 | 3 pack</v>
       </c>
       <c r="E198" t="str">
         <v>直柄钩</v>
@@ -9670,7 +9670,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D199" t="str">
-        <v>Shiner Upturned Eye | 4/0 | 4 pack</v>
+        <v>4/0 | 4 pack</v>
       </c>
       <c r="E199" t="str">
         <v>直柄钩</v>
@@ -9711,7 +9711,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D200" t="str">
-        <v>Shiner Upturned Eye | 4/0 | 5 pack</v>
+        <v>4/0 | 5 pack</v>
       </c>
       <c r="E200" t="str">
         <v>直柄钩</v>
@@ -9752,7 +9752,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D201" t="str">
-        <v>Shiner Upturned Eye | 4/0 | 6 pack</v>
+        <v>4/0 | 6 pack</v>
       </c>
       <c r="E201" t="str">
         <v>直柄钩</v>
@@ -9793,7 +9793,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D202" t="str">
-        <v>Shiner Upturned Eye | 4/0 | 7 pack</v>
+        <v>4/0 | 7 pack</v>
       </c>
       <c r="E202" t="str">
         <v>直柄钩</v>
@@ -9834,7 +9834,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D203" t="str">
-        <v>Shiner Upturned Eye | 4/0 | 8 pack</v>
+        <v>4/0 | 8 pack</v>
       </c>
       <c r="E203" t="str">
         <v>直柄钩</v>
@@ -9875,7 +9875,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D204" t="str">
-        <v>Shiner Upturned Eye | 5/0 | 25 pack</v>
+        <v>5/0 | 25 pack</v>
       </c>
       <c r="E204" t="str">
         <v>直柄钩</v>
@@ -9916,7 +9916,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D205" t="str">
-        <v>Shiner Upturned Eye | 5/0 | 3 pack</v>
+        <v>5/0 | 3 pack</v>
       </c>
       <c r="E205" t="str">
         <v>直柄钩</v>
@@ -9957,7 +9957,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D206" t="str">
-        <v>Shiner Upturned Eye | 5/0 | 4 pack</v>
+        <v>5/0 | 4 pack</v>
       </c>
       <c r="E206" t="str">
         <v>直柄钩</v>
@@ -9998,7 +9998,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D207" t="str">
-        <v>Shiner Upturned Eye | 5/0 | 5 pack</v>
+        <v>5/0 | 5 pack</v>
       </c>
       <c r="E207" t="str">
         <v>直柄钩</v>
@@ -10039,7 +10039,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D208" t="str">
-        <v>Shiner Upturned Eye | 5/0 | 6 pack</v>
+        <v>5/0 | 6 pack</v>
       </c>
       <c r="E208" t="str">
         <v>直柄钩</v>
@@ -10080,7 +10080,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D209" t="str">
-        <v>Shiner Upturned Eye | 5/0 | 7 pack</v>
+        <v>5/0 | 7 pack</v>
       </c>
       <c r="E209" t="str">
         <v>直柄钩</v>
@@ -10121,7 +10121,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D210" t="str">
-        <v>Shiner Upturned Eye | 5/0 | 8 pack</v>
+        <v>5/0 | 8 pack</v>
       </c>
       <c r="E210" t="str">
         <v>直柄钩</v>
@@ -10162,7 +10162,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D211" t="str">
-        <v>Shiner Upturned Eye | 6/0 | 25 pack</v>
+        <v>6/0 | 25 pack</v>
       </c>
       <c r="E211" t="str">
         <v>直柄钩</v>
@@ -10203,7 +10203,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D212" t="str">
-        <v>Shiner Upturned Eye | 6/0 | 3 pack</v>
+        <v>6/0 | 3 pack</v>
       </c>
       <c r="E212" t="str">
         <v>直柄钩</v>
@@ -10244,7 +10244,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D213" t="str">
-        <v>Shiner Upturned Eye | 6/0 | 4 pack</v>
+        <v>6/0 | 4 pack</v>
       </c>
       <c r="E213" t="str">
         <v>直柄钩</v>
@@ -10285,7 +10285,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D214" t="str">
-        <v>Shiner Upturned Eye | 6/0 | 5 pack</v>
+        <v>6/0 | 5 pack</v>
       </c>
       <c r="E214" t="str">
         <v>直柄钩</v>
@@ -10326,7 +10326,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D215" t="str">
-        <v>Shiner Upturned Eye | 6/0 | 6 pack</v>
+        <v>6/0 | 6 pack</v>
       </c>
       <c r="E215" t="str">
         <v>直柄钩</v>
@@ -10367,7 +10367,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D216" t="str">
-        <v>Shiner Upturned Eye | 6/0 | 7 pack</v>
+        <v>6/0 | 7 pack</v>
       </c>
       <c r="E216" t="str">
         <v>直柄钩</v>
@@ -10408,7 +10408,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D217" t="str">
-        <v>Shiner Upturned Eye | 6/0 | 8 pack</v>
+        <v>6/0 | 8 pack</v>
       </c>
       <c r="E217" t="str">
         <v>直柄钩</v>
@@ -10449,7 +10449,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D218" t="str">
-        <v>Shiner Straight Eye | 6 | 25 pack</v>
+        <v>6 | 25 pack</v>
       </c>
       <c r="E218" t="str">
         <v>直柄钩</v>
@@ -10490,7 +10490,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D219" t="str">
-        <v>Shiner Straight Eye | 6 | 3 pack</v>
+        <v>6 | 3 pack</v>
       </c>
       <c r="E219" t="str">
         <v>直柄钩</v>
@@ -10531,7 +10531,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D220" t="str">
-        <v>Shiner Straight Eye | 6 | 4 pack</v>
+        <v>6 | 4 pack</v>
       </c>
       <c r="E220" t="str">
         <v>直柄钩</v>
@@ -10572,7 +10572,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D221" t="str">
-        <v>Shiner Straight Eye | 6 | 5 pack</v>
+        <v>6 | 5 pack</v>
       </c>
       <c r="E221" t="str">
         <v>直柄钩</v>
@@ -10613,7 +10613,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D222" t="str">
-        <v>Shiner Straight Eye | 6 | 6 pack</v>
+        <v>6 | 6 pack</v>
       </c>
       <c r="E222" t="str">
         <v>直柄钩</v>
@@ -10654,7 +10654,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D223" t="str">
-        <v>Shiner Straight Eye | 6 | 7 pack</v>
+        <v>6 | 7 pack</v>
       </c>
       <c r="E223" t="str">
         <v>直柄钩</v>
@@ -10695,7 +10695,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D224" t="str">
-        <v>Shiner Straight Eye | 6 | 8 pack</v>
+        <v>6 | 8 pack</v>
       </c>
       <c r="E224" t="str">
         <v>直柄钩</v>
@@ -10736,7 +10736,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D225" t="str">
-        <v>Shiner Straight Eye | 4 | 25 pack</v>
+        <v>4 | 25 pack</v>
       </c>
       <c r="E225" t="str">
         <v>直柄钩</v>
@@ -10777,7 +10777,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D226" t="str">
-        <v>Shiner Straight Eye | 4 | 3 pack</v>
+        <v>4 | 3 pack</v>
       </c>
       <c r="E226" t="str">
         <v>直柄钩</v>
@@ -10818,7 +10818,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D227" t="str">
-        <v>Shiner Straight Eye | 4 | 4 pack</v>
+        <v>4 | 4 pack</v>
       </c>
       <c r="E227" t="str">
         <v>直柄钩</v>
@@ -10859,7 +10859,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D228" t="str">
-        <v>Shiner Straight Eye | 4 | 5 pack</v>
+        <v>4 | 5 pack</v>
       </c>
       <c r="E228" t="str">
         <v>直柄钩</v>
@@ -10900,7 +10900,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D229" t="str">
-        <v>Shiner Straight Eye | 4 | 6 pack</v>
+        <v>4 | 6 pack</v>
       </c>
       <c r="E229" t="str">
         <v>直柄钩</v>
@@ -10941,7 +10941,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D230" t="str">
-        <v>Shiner Straight Eye | 4 | 7 pack</v>
+        <v>4 | 7 pack</v>
       </c>
       <c r="E230" t="str">
         <v>直柄钩</v>
@@ -10982,7 +10982,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D231" t="str">
-        <v>Shiner Straight Eye | 4 | 8 pack</v>
+        <v>4 | 8 pack</v>
       </c>
       <c r="E231" t="str">
         <v>直柄钩</v>
@@ -11023,7 +11023,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D232" t="str">
-        <v>Shiner Straight Eye | 2 | 25 pack</v>
+        <v>2 | 25 pack</v>
       </c>
       <c r="E232" t="str">
         <v>直柄钩</v>
@@ -11064,7 +11064,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D233" t="str">
-        <v>Shiner Straight Eye | 2 | 3 pack</v>
+        <v>2 | 3 pack</v>
       </c>
       <c r="E233" t="str">
         <v>直柄钩</v>
@@ -11105,7 +11105,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D234" t="str">
-        <v>Shiner Straight Eye | 2 | 4 pack</v>
+        <v>2 | 4 pack</v>
       </c>
       <c r="E234" t="str">
         <v>直柄钩</v>
@@ -11146,7 +11146,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D235" t="str">
-        <v>Shiner Straight Eye | 2 | 5 pack</v>
+        <v>2 | 5 pack</v>
       </c>
       <c r="E235" t="str">
         <v>直柄钩</v>
@@ -11187,7 +11187,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D236" t="str">
-        <v>Shiner Straight Eye | 2 | 6 pack</v>
+        <v>2 | 6 pack</v>
       </c>
       <c r="E236" t="str">
         <v>直柄钩</v>
@@ -11228,7 +11228,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D237" t="str">
-        <v>Shiner Straight Eye | 2 | 7 pack</v>
+        <v>2 | 7 pack</v>
       </c>
       <c r="E237" t="str">
         <v>直柄钩</v>
@@ -11269,7 +11269,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D238" t="str">
-        <v>Shiner Straight Eye | 2 | 8 pack</v>
+        <v>2 | 8 pack</v>
       </c>
       <c r="E238" t="str">
         <v>直柄钩</v>
@@ -11310,7 +11310,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D239" t="str">
-        <v>Shiner Straight Eye | 1 | 25 pack</v>
+        <v>1 | 25 pack</v>
       </c>
       <c r="E239" t="str">
         <v>直柄钩</v>
@@ -11351,7 +11351,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D240" t="str">
-        <v>Shiner Straight Eye | 1 | 3 pack</v>
+        <v>1 | 3 pack</v>
       </c>
       <c r="E240" t="str">
         <v>直柄钩</v>
@@ -11392,7 +11392,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D241" t="str">
-        <v>Shiner Straight Eye | 1 | 4 pack</v>
+        <v>1 | 4 pack</v>
       </c>
       <c r="E241" t="str">
         <v>直柄钩</v>
@@ -11433,7 +11433,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D242" t="str">
-        <v>Shiner Straight Eye | 1 | 5 pack</v>
+        <v>1 | 5 pack</v>
       </c>
       <c r="E242" t="str">
         <v>直柄钩</v>
@@ -11474,7 +11474,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D243" t="str">
-        <v>Shiner Straight Eye | 1 | 6 pack</v>
+        <v>1 | 6 pack</v>
       </c>
       <c r="E243" t="str">
         <v>直柄钩</v>
@@ -11515,7 +11515,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D244" t="str">
-        <v>Shiner Straight Eye | 1 | 7 pack</v>
+        <v>1 | 7 pack</v>
       </c>
       <c r="E244" t="str">
         <v>直柄钩</v>
@@ -11556,7 +11556,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D245" t="str">
-        <v>Shiner Straight Eye | 1 | 8 pack</v>
+        <v>1 | 8 pack</v>
       </c>
       <c r="E245" t="str">
         <v>直柄钩</v>
@@ -11597,7 +11597,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D246" t="str">
-        <v>Shiner Straight Eye | 1/0 | 25 pack</v>
+        <v>1/0 | 25 pack</v>
       </c>
       <c r="E246" t="str">
         <v>直柄钩</v>
@@ -11638,7 +11638,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D247" t="str">
-        <v>Shiner Straight Eye | 1/0 | 3 pack</v>
+        <v>1/0 | 3 pack</v>
       </c>
       <c r="E247" t="str">
         <v>直柄钩</v>
@@ -11679,7 +11679,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D248" t="str">
-        <v>Shiner Straight Eye | 1/0 | 4 pack</v>
+        <v>1/0 | 4 pack</v>
       </c>
       <c r="E248" t="str">
         <v>直柄钩</v>
@@ -11720,7 +11720,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D249" t="str">
-        <v>Shiner Straight Eye | 1/0 | 5 pack</v>
+        <v>1/0 | 5 pack</v>
       </c>
       <c r="E249" t="str">
         <v>直柄钩</v>
@@ -11761,7 +11761,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D250" t="str">
-        <v>Shiner Straight Eye | 1/0 | 6 pack</v>
+        <v>1/0 | 6 pack</v>
       </c>
       <c r="E250" t="str">
         <v>直柄钩</v>
@@ -11802,7 +11802,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D251" t="str">
-        <v>Shiner Straight Eye | 1/0 | 7 pack</v>
+        <v>1/0 | 7 pack</v>
       </c>
       <c r="E251" t="str">
         <v>直柄钩</v>
@@ -11843,7 +11843,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D252" t="str">
-        <v>Shiner Straight Eye | 1/0 | 8 pack</v>
+        <v>1/0 | 8 pack</v>
       </c>
       <c r="E252" t="str">
         <v>直柄钩</v>
@@ -11884,7 +11884,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D253" t="str">
-        <v>Shiner Straight Eye | 2/0 | 25 pack</v>
+        <v>2/0 | 25 pack</v>
       </c>
       <c r="E253" t="str">
         <v>直柄钩</v>
@@ -11925,7 +11925,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D254" t="str">
-        <v>Shiner Straight Eye | 2/0 | 3 pack</v>
+        <v>2/0 | 3 pack</v>
       </c>
       <c r="E254" t="str">
         <v>直柄钩</v>
@@ -11966,7 +11966,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D255" t="str">
-        <v>Shiner Straight Eye | 2/0 | 4 pack</v>
+        <v>2/0 | 4 pack</v>
       </c>
       <c r="E255" t="str">
         <v>直柄钩</v>
@@ -12007,7 +12007,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D256" t="str">
-        <v>Shiner Straight Eye | 2/0 | 5 pack</v>
+        <v>2/0 | 5 pack</v>
       </c>
       <c r="E256" t="str">
         <v>直柄钩</v>
@@ -12048,7 +12048,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D257" t="str">
-        <v>Shiner Straight Eye | 2/0 | 6 pack</v>
+        <v>2/0 | 6 pack</v>
       </c>
       <c r="E257" t="str">
         <v>直柄钩</v>
@@ -12089,7 +12089,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D258" t="str">
-        <v>Shiner Straight Eye | 2/0 | 7 pack</v>
+        <v>2/0 | 7 pack</v>
       </c>
       <c r="E258" t="str">
         <v>直柄钩</v>
@@ -12130,7 +12130,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D259" t="str">
-        <v>Shiner Straight Eye | 2/0 | 8 pack</v>
+        <v>2/0 | 8 pack</v>
       </c>
       <c r="E259" t="str">
         <v>直柄钩</v>
@@ -12171,7 +12171,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D260" t="str">
-        <v>Shiner Straight Eye | 3/0 | 25 pack</v>
+        <v>3/0 | 25 pack</v>
       </c>
       <c r="E260" t="str">
         <v>直柄钩</v>
@@ -12212,7 +12212,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D261" t="str">
-        <v>Shiner Straight Eye | 3/0 | 3 pack</v>
+        <v>3/0 | 3 pack</v>
       </c>
       <c r="E261" t="str">
         <v>直柄钩</v>
@@ -12253,7 +12253,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D262" t="str">
-        <v>Shiner Straight Eye | 3/0 | 4 pack</v>
+        <v>3/0 | 4 pack</v>
       </c>
       <c r="E262" t="str">
         <v>直柄钩</v>
@@ -12294,7 +12294,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D263" t="str">
-        <v>Shiner Straight Eye | 3/0 | 5 pack</v>
+        <v>3/0 | 5 pack</v>
       </c>
       <c r="E263" t="str">
         <v>直柄钩</v>
@@ -12335,7 +12335,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D264" t="str">
-        <v>Shiner Straight Eye | 3/0 | 6 pack</v>
+        <v>3/0 | 6 pack</v>
       </c>
       <c r="E264" t="str">
         <v>直柄钩</v>
@@ -12376,7 +12376,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D265" t="str">
-        <v>Shiner Straight Eye | 3/0 | 7 pack</v>
+        <v>3/0 | 7 pack</v>
       </c>
       <c r="E265" t="str">
         <v>直柄钩</v>
@@ -12417,7 +12417,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D266" t="str">
-        <v>Shiner Straight Eye | 3/0 | 8 pack</v>
+        <v>3/0 | 8 pack</v>
       </c>
       <c r="E266" t="str">
         <v>直柄钩</v>
@@ -12458,7 +12458,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D267" t="str">
-        <v>Shiner Straight Eye | 4/0 | 25 pack</v>
+        <v>4/0 | 25 pack</v>
       </c>
       <c r="E267" t="str">
         <v>直柄钩</v>
@@ -12499,7 +12499,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D268" t="str">
-        <v>Shiner Straight Eye | 4/0 | 3 pack</v>
+        <v>4/0 | 3 pack</v>
       </c>
       <c r="E268" t="str">
         <v>直柄钩</v>
@@ -12540,7 +12540,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D269" t="str">
-        <v>Shiner Straight Eye | 4/0 | 4 pack</v>
+        <v>4/0 | 4 pack</v>
       </c>
       <c r="E269" t="str">
         <v>直柄钩</v>
@@ -12581,7 +12581,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D270" t="str">
-        <v>Shiner Straight Eye | 4/0 | 5 pack</v>
+        <v>4/0 | 5 pack</v>
       </c>
       <c r="E270" t="str">
         <v>直柄钩</v>
@@ -12622,7 +12622,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D271" t="str">
-        <v>Shiner Straight Eye | 4/0 | 6 pack</v>
+        <v>4/0 | 6 pack</v>
       </c>
       <c r="E271" t="str">
         <v>直柄钩</v>
@@ -12663,7 +12663,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D272" t="str">
-        <v>Shiner Straight Eye | 4/0 | 7 pack</v>
+        <v>4/0 | 7 pack</v>
       </c>
       <c r="E272" t="str">
         <v>直柄钩</v>
@@ -12704,7 +12704,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D273" t="str">
-        <v>Shiner Straight Eye | 4/0 | 8 pack</v>
+        <v>4/0 | 8 pack</v>
       </c>
       <c r="E273" t="str">
         <v>直柄钩</v>
@@ -12745,7 +12745,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D274" t="str">
-        <v>Shiner Straight Eye | 5/0 | 25 pack</v>
+        <v>5/0 | 25 pack</v>
       </c>
       <c r="E274" t="str">
         <v>直柄钩</v>
@@ -12786,7 +12786,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D275" t="str">
-        <v>Shiner Straight Eye | 5/0 | 3 pack</v>
+        <v>5/0 | 3 pack</v>
       </c>
       <c r="E275" t="str">
         <v>直柄钩</v>
@@ -12827,7 +12827,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D276" t="str">
-        <v>Shiner Straight Eye | 5/0 | 4 pack</v>
+        <v>5/0 | 4 pack</v>
       </c>
       <c r="E276" t="str">
         <v>直柄钩</v>
@@ -12868,7 +12868,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D277" t="str">
-        <v>Shiner Straight Eye | 5/0 | 5 pack</v>
+        <v>5/0 | 5 pack</v>
       </c>
       <c r="E277" t="str">
         <v>直柄钩</v>
@@ -12909,7 +12909,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D278" t="str">
-        <v>Shiner Straight Eye | 5/0 | 6 pack</v>
+        <v>5/0 | 6 pack</v>
       </c>
       <c r="E278" t="str">
         <v>直柄钩</v>
@@ -12950,7 +12950,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D279" t="str">
-        <v>Shiner Straight Eye | 5/0 | 7 pack</v>
+        <v>5/0 | 7 pack</v>
       </c>
       <c r="E279" t="str">
         <v>直柄钩</v>
@@ -12991,7 +12991,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D280" t="str">
-        <v>Shiner Straight Eye | 5/0 | 8 pack</v>
+        <v>5/0 | 8 pack</v>
       </c>
       <c r="E280" t="str">
         <v>直柄钩</v>
@@ -13032,7 +13032,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D281" t="str">
-        <v>Shiner Straight Eye | 6/0 | 25 pack</v>
+        <v>6/0 | 25 pack</v>
       </c>
       <c r="E281" t="str">
         <v>直柄钩</v>
@@ -13073,7 +13073,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D282" t="str">
-        <v>Shiner Straight Eye | 6/0 | 3 pack</v>
+        <v>6/0 | 3 pack</v>
       </c>
       <c r="E282" t="str">
         <v>直柄钩</v>
@@ -13114,7 +13114,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D283" t="str">
-        <v>Shiner Straight Eye | 6/0 | 4 pack</v>
+        <v>6/0 | 4 pack</v>
       </c>
       <c r="E283" t="str">
         <v>直柄钩</v>
@@ -13155,7 +13155,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D284" t="str">
-        <v>Shiner Straight Eye | 6/0 | 5 pack</v>
+        <v>6/0 | 5 pack</v>
       </c>
       <c r="E284" t="str">
         <v>直柄钩</v>
@@ -13196,7 +13196,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D285" t="str">
-        <v>Shiner Straight Eye | 6/0 | 6 pack</v>
+        <v>6/0 | 6 pack</v>
       </c>
       <c r="E285" t="str">
         <v>直柄钩</v>
@@ -13237,7 +13237,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D286" t="str">
-        <v>Shiner Straight Eye | 6/0 | 7 pack</v>
+        <v>6/0 | 7 pack</v>
       </c>
       <c r="E286" t="str">
         <v>直柄钩</v>
@@ -13278,7 +13278,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D287" t="str">
-        <v>Shiner Straight Eye | 6/0 | 8 pack</v>
+        <v>6/0 | 8 pack</v>
       </c>
       <c r="E287" t="str">
         <v>直柄钩</v>
@@ -13319,7 +13319,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D288" t="str">
-        <v>Micro Wide Gap | 10 | 10 pack</v>
+        <v>10 | 10 pack</v>
       </c>
       <c r="E288" t="str">
         <v>曲柄钩</v>
@@ -13360,7 +13360,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D289" t="str">
-        <v>Micro Wide Gap | 8 | 10 pack</v>
+        <v>8 | 10 pack</v>
       </c>
       <c r="E289" t="str">
         <v>曲柄钩</v>
@@ -13401,7 +13401,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D290" t="str">
-        <v>Micro Wide Gap | 6 | 10 pack</v>
+        <v>6 | 10 pack</v>
       </c>
       <c r="E290" t="str">
         <v>曲柄钩</v>
@@ -13442,7 +13442,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D291" t="str">
-        <v>Micro V Gap | 12 | 10 pack</v>
+        <v>12 | 10 pack</v>
       </c>
       <c r="E291" t="str">
         <v>曲柄钩</v>
@@ -13483,7 +13483,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D292" t="str">
-        <v>Micro V Gap | 10 | 10 pack</v>
+        <v>10 | 10 pack</v>
       </c>
       <c r="E292" t="str">
         <v>曲柄钩</v>
@@ -13524,7 +13524,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D293" t="str">
-        <v>Micro V Gap | 8 | 10 pack</v>
+        <v>8 | 10 pack</v>
       </c>
       <c r="E293" t="str">
         <v>曲柄钩</v>
@@ -13565,7 +13565,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D294" t="str">
-        <v>Micro V Gap | 6 | 10 pack</v>
+        <v>6 | 10 pack</v>
       </c>
       <c r="E294" t="str">
         <v>曲柄钩</v>
@@ -13606,7 +13606,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D295" t="str">
-        <v>Micro Perfect Gap | 12 | 10 pack</v>
+        <v>12 | 10 pack</v>
       </c>
       <c r="E295" t="str">
         <v>曲柄钩</v>
@@ -13647,7 +13647,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D296" t="str">
-        <v>Micro Perfect Gap | 10 | 10 pack</v>
+        <v>10 | 10 pack</v>
       </c>
       <c r="E296" t="str">
         <v>曲柄钩</v>
@@ -13688,7 +13688,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D297" t="str">
-        <v>Micro Perfect Gap | 8 | 10 pack</v>
+        <v>8 | 10 pack</v>
       </c>
       <c r="E297" t="str">
         <v>曲柄钩</v>
@@ -13729,7 +13729,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D298" t="str">
-        <v>Micro Perfect Gap | 6 | 10 pack</v>
+        <v>6 | 10 pack</v>
       </c>
       <c r="E298" t="str">
         <v>曲柄钩</v>
@@ -13770,7 +13770,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D299" t="str">
-        <v>Micro Perfect Gap | 4 | 10 pack</v>
+        <v>4 | 10 pack</v>
       </c>
       <c r="E299" t="str">
         <v>曲柄钩</v>
@@ -13811,7 +13811,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D300" t="str">
-        <v>G-Stinger | 2 | 4 pack</v>
+        <v>2 | 4 pack</v>
       </c>
       <c r="E300" t="str">
         <v>挂钩</v>
@@ -13852,7 +13852,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D301" t="str">
-        <v>G-Stinger | 1 | 4 pack</v>
+        <v>1 | 4 pack</v>
       </c>
       <c r="E301" t="str">
         <v>挂钩</v>
@@ -13893,7 +13893,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D302" t="str">
-        <v>G-Stinger | 1/0 | 4 pack</v>
+        <v>1/0 | 4 pack</v>
       </c>
       <c r="E302" t="str">
         <v>挂钩</v>
@@ -13934,7 +13934,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D303" t="str">
-        <v>G-Carp Super Hook | 10 | 10 pack</v>
+        <v>10 | 10 pack</v>
       </c>
       <c r="E303" t="str">
         <v>鲤鱼钩</v>
@@ -13975,7 +13975,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D304" t="str">
-        <v>G-Carp Super Hook | 8 | 10 pack</v>
+        <v>8 | 10 pack</v>
       </c>
       <c r="E304" t="str">
         <v>鲤鱼钩</v>
@@ -14016,7 +14016,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D305" t="str">
-        <v>G-Carp Super Hook | 6 | 10 pack</v>
+        <v>6 | 10 pack</v>
       </c>
       <c r="E305" t="str">
         <v>鲤鱼钩</v>
@@ -14057,7 +14057,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D306" t="str">
-        <v>G-Carp Super Hook | 4 | 10 pack</v>
+        <v>4 | 10 pack</v>
       </c>
       <c r="E306" t="str">
         <v>鲤鱼钩</v>
@@ -14098,7 +14098,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D307" t="str">
-        <v>G-Carp Super Hook | 2 | 10 pack</v>
+        <v>2 | 10 pack</v>
       </c>
       <c r="E307" t="str">
         <v>鲤鱼钩</v>
@@ -14139,7 +14139,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D308" t="str">
-        <v>G-Carp Super Hook | 1 | 10 pack</v>
+        <v>1 | 10 pack</v>
       </c>
       <c r="E308" t="str">
         <v>鲤鱼钩</v>
@@ -14180,7 +14180,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D309" t="str">
-        <v>G-Carp Specialist RX | 12 | 10 pack</v>
+        <v>12 | 10 pack</v>
       </c>
       <c r="E309" t="str">
         <v>鲤鱼钩</v>
@@ -14221,7 +14221,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D310" t="str">
-        <v>G-Carp Specialist RX | 10 | 10 pack</v>
+        <v>10 | 10 pack</v>
       </c>
       <c r="E310" t="str">
         <v>鲤鱼钩</v>
@@ -14262,7 +14262,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D311" t="str">
-        <v>G-Carp Specialist RX | 8 | 10 pack</v>
+        <v>8 | 10 pack</v>
       </c>
       <c r="E311" t="str">
         <v>鲤鱼钩</v>
@@ -14303,7 +14303,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D312" t="str">
-        <v>G-Carp Specialist RX | 6 | 10 pack</v>
+        <v>6 | 10 pack</v>
       </c>
       <c r="E312" t="str">
         <v>鲤鱼钩</v>
@@ -14344,7 +14344,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D313" t="str">
-        <v>G-Carp Specialist RX | 4 | 10 pack</v>
+        <v>4 | 10 pack</v>
       </c>
       <c r="E313" t="str">
         <v>鲤鱼钩</v>
@@ -14385,7 +14385,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D314" t="str">
-        <v>G-Carp Specialist RX | 2 | 10 pack</v>
+        <v>2 | 10 pack</v>
       </c>
       <c r="E314" t="str">
         <v>鲤鱼钩</v>
@@ -14426,7 +14426,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D315" t="str">
-        <v>G-Carp Specialist R | 12 | 10 pack</v>
+        <v>12 | 10 pack</v>
       </c>
       <c r="E315" t="str">
         <v>鲤鱼钩</v>
@@ -14467,7 +14467,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D316" t="str">
-        <v>G-Carp Specialist R | 10 | 10 pack</v>
+        <v>10 | 10 pack</v>
       </c>
       <c r="E316" t="str">
         <v>鲤鱼钩</v>
@@ -14508,7 +14508,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D317" t="str">
-        <v>G-Carp Specialist R | 8 | 10 pack</v>
+        <v>8 | 10 pack</v>
       </c>
       <c r="E317" t="str">
         <v>鲤鱼钩</v>
@@ -14549,7 +14549,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D318" t="str">
-        <v>G-Carp Specialist R | 6 | 10 pack</v>
+        <v>6 | 10 pack</v>
       </c>
       <c r="E318" t="str">
         <v>鲤鱼钩</v>
@@ -14590,7 +14590,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D319" t="str">
-        <v>G-Carp Specialist R | 4 | 10 pack</v>
+        <v>4 | 10 pack</v>
       </c>
       <c r="E319" t="str">
         <v>鲤鱼钩</v>
@@ -14631,7 +14631,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D320" t="str">
-        <v>G-Carp Specialist R | 2 | 10 pack</v>
+        <v>2 | 10 pack</v>
       </c>
       <c r="E320" t="str">
         <v>鲤鱼钩</v>
@@ -14672,7 +14672,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D321" t="str">
-        <v>G-Carp Hump Back | 10 | 10 pack</v>
+        <v>10 | 10 pack</v>
       </c>
       <c r="E321" t="str">
         <v>鲤鱼钩</v>
@@ -14713,7 +14713,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D322" t="str">
-        <v>G-Carp Hump Back | 8 | 10 pack</v>
+        <v>8 | 10 pack</v>
       </c>
       <c r="E322" t="str">
         <v>鲤鱼钩</v>
@@ -14754,7 +14754,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D323" t="str">
-        <v>G-Carp Hump Back | 6 | 10 pack</v>
+        <v>6 | 10 pack</v>
       </c>
       <c r="E323" t="str">
         <v>鲤鱼钩</v>
@@ -14795,7 +14795,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D324" t="str">
-        <v>G-Carp Hump Back | 4 | 10 pack</v>
+        <v>4 | 10 pack</v>
       </c>
       <c r="E324" t="str">
         <v>鲤鱼钩</v>
@@ -14836,7 +14836,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D325" t="str">
-        <v>G-Carp Hump Back | 2 | 10 pack</v>
+        <v>2 | 10 pack</v>
       </c>
       <c r="E325" t="str">
         <v>鲤鱼钩</v>
@@ -14877,7 +14877,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D326" t="str">
-        <v>Finesse Wide Gap Weedless | 4 | 4 pack</v>
+        <v>4 | 4 pack</v>
       </c>
       <c r="E326" t="str">
         <v>曲柄钩</v>
@@ -14918,7 +14918,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D327" t="str">
-        <v>Finesse Wide Gap Weedless | 4 | 5 pack</v>
+        <v>4 | 5 pack</v>
       </c>
       <c r="E327" t="str">
         <v>曲柄钩</v>
@@ -14959,7 +14959,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D328" t="str">
-        <v>Finesse Wide Gap Weedless | 2 | 4 pack</v>
+        <v>2 | 4 pack</v>
       </c>
       <c r="E328" t="str">
         <v>曲柄钩</v>
@@ -15000,7 +15000,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D329" t="str">
-        <v>Finesse Wide Gap Weedless | 2 | 5 pack</v>
+        <v>2 | 5 pack</v>
       </c>
       <c r="E329" t="str">
         <v>曲柄钩</v>
@@ -15041,7 +15041,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D330" t="str">
-        <v>Finesse Wide Gap Weedless | 1 | 4 pack</v>
+        <v>1 | 4 pack</v>
       </c>
       <c r="E330" t="str">
         <v>曲柄钩</v>
@@ -15082,7 +15082,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D331" t="str">
-        <v>Finesse Wide Gap Weedless | 1 | 5 pack</v>
+        <v>1 | 5 pack</v>
       </c>
       <c r="E331" t="str">
         <v>曲柄钩</v>
@@ -15123,7 +15123,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D332" t="str">
-        <v>Finesse Wide Gap Weedless | 1/0 | 4 pack</v>
+        <v>1/0 | 4 pack</v>
       </c>
       <c r="E332" t="str">
         <v>曲柄钩</v>
@@ -15164,7 +15164,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D333" t="str">
-        <v>Finesse Wide Gap Weedless | 1/0 | 5 pack</v>
+        <v>1/0 | 5 pack</v>
       </c>
       <c r="E333" t="str">
         <v>曲柄钩</v>
@@ -15205,7 +15205,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D334" t="str">
-        <v>Finesse Wide Gap Weedless | 2/0 | 4 pack</v>
+        <v>2/0 | 4 pack</v>
       </c>
       <c r="E334" t="str">
         <v>曲柄钩</v>
@@ -15246,7 +15246,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D335" t="str">
-        <v>Finesse Wide Gap Weedless | 2/0 | 5 pack</v>
+        <v>2/0 | 5 pack</v>
       </c>
       <c r="E335" t="str">
         <v>曲柄钩</v>
@@ -15287,7 +15287,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D336" t="str">
-        <v>Finesse Wide Gap Weedless | 3/0 | 4 pack</v>
+        <v>3/0 | 4 pack</v>
       </c>
       <c r="E336" t="str">
         <v>曲柄钩</v>
@@ -15328,7 +15328,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D337" t="str">
-        <v>Finesse Wide Gap Weedless | 3/0 | 5 pack</v>
+        <v>3/0 | 5 pack</v>
       </c>
       <c r="E337" t="str">
         <v>曲柄钩</v>
@@ -15369,7 +15369,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D338" t="str">
-        <v>Finesse Wide Gap Weedless | 4/0 | 4 pack</v>
+        <v>4/0 | 4 pack</v>
       </c>
       <c r="E338" t="str">
         <v>曲柄钩</v>
@@ -15410,7 +15410,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D339" t="str">
-        <v>Finesse Wide Gap Weedless | 4/0 | 5 pack</v>
+        <v>4/0 | 5 pack</v>
       </c>
       <c r="E339" t="str">
         <v>曲柄钩</v>
@@ -15451,7 +15451,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D340" t="str">
-        <v>Finesse Wide Gap Weedless | 5/0 | 4 pack</v>
+        <v>5/0 | 4 pack</v>
       </c>
       <c r="E340" t="str">
         <v>曲柄钩</v>
@@ -15492,7 +15492,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D341" t="str">
-        <v>Finesse Wide Gap Weedless | 5/0 | 5 pack</v>
+        <v>5/0 | 5 pack</v>
       </c>
       <c r="E341" t="str">
         <v>曲柄钩</v>
@@ -15533,7 +15533,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D342" t="str">
-        <v>Finesse Wide Gap Weedless | 6/0 | 4 pack</v>
+        <v>6/0 | 4 pack</v>
       </c>
       <c r="E342" t="str">
         <v>曲柄钩</v>
@@ -15574,7 +15574,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D343" t="str">
-        <v>Finesse Wide Gap Weedless | 6/0 | 5 pack</v>
+        <v>6/0 | 5 pack</v>
       </c>
       <c r="E343" t="str">
         <v>曲柄钩</v>
@@ -15615,7 +15615,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D344" t="str">
-        <v>Finesse Wide Gap | 4 | 25 pack</v>
+        <v>4 | 25 pack</v>
       </c>
       <c r="E344" t="str">
         <v>曲柄钩</v>
@@ -15656,7 +15656,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D345" t="str">
-        <v>Finesse Wide Gap | 4 | 5 pack</v>
+        <v>4 | 5 pack</v>
       </c>
       <c r="E345" t="str">
         <v>曲柄钩</v>
@@ -15697,7 +15697,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D346" t="str">
-        <v>Finesse Wide Gap | 4 | 6 pack</v>
+        <v>4 | 6 pack</v>
       </c>
       <c r="E346" t="str">
         <v>曲柄钩</v>
@@ -15738,7 +15738,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D347" t="str">
-        <v>Finesse Wide Gap | 2 | 25 pack</v>
+        <v>2 | 25 pack</v>
       </c>
       <c r="E347" t="str">
         <v>曲柄钩</v>
@@ -15779,7 +15779,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D348" t="str">
-        <v>Finesse Wide Gap | 2 | 5 pack</v>
+        <v>2 | 5 pack</v>
       </c>
       <c r="E348" t="str">
         <v>曲柄钩</v>
@@ -15820,7 +15820,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D349" t="str">
-        <v>Finesse Wide Gap | 2 | 6 pack</v>
+        <v>2 | 6 pack</v>
       </c>
       <c r="E349" t="str">
         <v>曲柄钩</v>
@@ -15861,7 +15861,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D350" t="str">
-        <v>Finesse Wide Gap | 1 | 25 pack</v>
+        <v>1 | 25 pack</v>
       </c>
       <c r="E350" t="str">
         <v>曲柄钩</v>
@@ -15902,7 +15902,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D351" t="str">
-        <v>Finesse Wide Gap | 1 | 5 pack</v>
+        <v>1 | 5 pack</v>
       </c>
       <c r="E351" t="str">
         <v>曲柄钩</v>
@@ -15943,7 +15943,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D352" t="str">
-        <v>Finesse Wide Gap | 1 | 6 pack</v>
+        <v>1 | 6 pack</v>
       </c>
       <c r="E352" t="str">
         <v>曲柄钩</v>
@@ -15984,7 +15984,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D353" t="str">
-        <v>Finesse Wide Gap | 1/0 | 25 pack</v>
+        <v>1/0 | 25 pack</v>
       </c>
       <c r="E353" t="str">
         <v>曲柄钩</v>
@@ -16025,7 +16025,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D354" t="str">
-        <v>Finesse Wide Gap | 1/0 | 5 pack</v>
+        <v>1/0 | 5 pack</v>
       </c>
       <c r="E354" t="str">
         <v>曲柄钩</v>
@@ -16066,7 +16066,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D355" t="str">
-        <v>Finesse Wide Gap | 1/0 | 6 pack</v>
+        <v>1/0 | 6 pack</v>
       </c>
       <c r="E355" t="str">
         <v>曲柄钩</v>
@@ -16107,7 +16107,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D356" t="str">
-        <v>Finesse Wide Gap | 2/0 | 25 pack</v>
+        <v>2/0 | 25 pack</v>
       </c>
       <c r="E356" t="str">
         <v>曲柄钩</v>
@@ -16148,7 +16148,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D357" t="str">
-        <v>Finesse Wide Gap | 2/0 | 5 pack</v>
+        <v>2/0 | 5 pack</v>
       </c>
       <c r="E357" t="str">
         <v>曲柄钩</v>
@@ -16189,7 +16189,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D358" t="str">
-        <v>Finesse Wide Gap | 2/0 | 6 pack</v>
+        <v>2/0 | 6 pack</v>
       </c>
       <c r="E358" t="str">
         <v>曲柄钩</v>
@@ -16230,7 +16230,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D359" t="str">
-        <v>Finesse Wide Gap | 3/0 | 25 pack</v>
+        <v>3/0 | 25 pack</v>
       </c>
       <c r="E359" t="str">
         <v>曲柄钩</v>
@@ -16271,7 +16271,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D360" t="str">
-        <v>Finesse Wide Gap | 3/0 | 5 pack</v>
+        <v>3/0 | 5 pack</v>
       </c>
       <c r="E360" t="str">
         <v>曲柄钩</v>
@@ -16312,7 +16312,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D361" t="str">
-        <v>Finesse Wide Gap | 3/0 | 6 pack</v>
+        <v>3/0 | 6 pack</v>
       </c>
       <c r="E361" t="str">
         <v>曲柄钩</v>
@@ -16353,7 +16353,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D362" t="str">
-        <v>Finesse Wide Gap | 4/0 | 25 pack</v>
+        <v>4/0 | 25 pack</v>
       </c>
       <c r="E362" t="str">
         <v>曲柄钩</v>
@@ -16394,7 +16394,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D363" t="str">
-        <v>Finesse Wide Gap | 4/0 | 5 pack</v>
+        <v>4/0 | 5 pack</v>
       </c>
       <c r="E363" t="str">
         <v>曲柄钩</v>
@@ -16435,7 +16435,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D364" t="str">
-        <v>Finesse Wide Gap | 4/0 | 6 pack</v>
+        <v>4/0 | 6 pack</v>
       </c>
       <c r="E364" t="str">
         <v>曲柄钩</v>
@@ -16476,7 +16476,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D365" t="str">
-        <v>Finesse Wide Gap | 5/0 | 25 pack</v>
+        <v>5/0 | 25 pack</v>
       </c>
       <c r="E365" t="str">
         <v>曲柄钩</v>
@@ -16517,7 +16517,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D366" t="str">
-        <v>Finesse Wide Gap | 5/0 | 5 pack</v>
+        <v>5/0 | 5 pack</v>
       </c>
       <c r="E366" t="str">
         <v>曲柄钩</v>
@@ -16558,7 +16558,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D367" t="str">
-        <v>Finesse Wide Gap | 5/0 | 6 pack</v>
+        <v>5/0 | 6 pack</v>
       </c>
       <c r="E367" t="str">
         <v>曲柄钩</v>
@@ -16599,7 +16599,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D368" t="str">
-        <v>Finesse Wide Gap | 6/0 | 25 pack</v>
+        <v>6/0 | 25 pack</v>
       </c>
       <c r="E368" t="str">
         <v>曲柄钩</v>
@@ -16640,7 +16640,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D369" t="str">
-        <v>Finesse Wide Gap | 6/0 | 5 pack</v>
+        <v>6/0 | 5 pack</v>
       </c>
       <c r="E369" t="str">
         <v>曲柄钩</v>
@@ -16681,7 +16681,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D370" t="str">
-        <v>Finesse Wide Gap | 6/0 | 6 pack</v>
+        <v>6/0 | 6 pack</v>
       </c>
       <c r="E370" t="str">
         <v>曲柄钩</v>
@@ -16722,7 +16722,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D371" t="str">
-        <v>Crappie Assortment | 8 | 15 pack</v>
+        <v>8 | 15 pack</v>
       </c>
       <c r="E371" t="str">
         <v>组合钩</v>
@@ -16763,7 +16763,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D372" t="str">
-        <v>Crappie Assortment | 6 | 15 pack</v>
+        <v>6 | 15 pack</v>
       </c>
       <c r="E372" t="str">
         <v>组合钩</v>
@@ -16804,7 +16804,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D373" t="str">
-        <v>Crappie Assortment | 4 | 15 pack</v>
+        <v>4 | 15 pack</v>
       </c>
       <c r="E373" t="str">
         <v>组合钩</v>
@@ -16845,7 +16845,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D374" t="str">
-        <v>Crappie Assortment | 2 | 15 pack</v>
+        <v>2 | 15 pack</v>
       </c>
       <c r="E374" t="str">
         <v>组合钩</v>
@@ -16886,7 +16886,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D375" t="str">
-        <v>Catfish Assortment | 1/0 | 20 pack</v>
+        <v>1/0 | 20 pack</v>
       </c>
       <c r="E375" t="str">
         <v>组合钩</v>
@@ -16927,7 +16927,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D376" t="str">
-        <v>Catfish Assortment | 4/0 | 20 pack</v>
+        <v>4/0 | 20 pack</v>
       </c>
       <c r="E376" t="str">
         <v>组合钩</v>
@@ -16968,7 +16968,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D377" t="str">
-        <v>Catfish Assortment | 6/0 | 20 pack</v>
+        <v>6/0 | 20 pack</v>
       </c>
       <c r="E377" t="str">
         <v>组合钩</v>
@@ -17009,7 +17009,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D378" t="str">
-        <v>Catfish Assortment | 8/0 | 20 pack</v>
+        <v>8/0 | 20 pack</v>
       </c>
       <c r="E378" t="str">
         <v>组合钩</v>
@@ -17050,7 +17050,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D379" t="str">
-        <v>Big Cat Circle | 1/0 | 25 pack</v>
+        <v>1/0 | 25 pack</v>
       </c>
       <c r="E379" t="str">
         <v>圆钩</v>
@@ -17091,7 +17091,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D380" t="str">
-        <v>Big Cat Circle | 1/0 | 3 pack</v>
+        <v>1/0 | 3 pack</v>
       </c>
       <c r="E380" t="str">
         <v>圆钩</v>
@@ -17132,7 +17132,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D381" t="str">
-        <v>Big Cat Circle | 1/0 | 5 pack</v>
+        <v>1/0 | 5 pack</v>
       </c>
       <c r="E381" t="str">
         <v>圆钩</v>
@@ -17173,7 +17173,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D382" t="str">
-        <v>Big Cat Circle | 1/0 | 6 pack</v>
+        <v>1/0 | 6 pack</v>
       </c>
       <c r="E382" t="str">
         <v>圆钩</v>
@@ -17214,7 +17214,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D383" t="str">
-        <v>Big Cat Circle | 2/0 | 25 pack</v>
+        <v>2/0 | 25 pack</v>
       </c>
       <c r="E383" t="str">
         <v>圆钩</v>
@@ -17255,7 +17255,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D384" t="str">
-        <v>Big Cat Circle | 2/0 | 3 pack</v>
+        <v>2/0 | 3 pack</v>
       </c>
       <c r="E384" t="str">
         <v>圆钩</v>
@@ -17296,7 +17296,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D385" t="str">
-        <v>Big Cat Circle | 2/0 | 5 pack</v>
+        <v>2/0 | 5 pack</v>
       </c>
       <c r="E385" t="str">
         <v>圆钩</v>
@@ -17337,7 +17337,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D386" t="str">
-        <v>Big Cat Circle | 2/0 | 6 pack</v>
+        <v>2/0 | 6 pack</v>
       </c>
       <c r="E386" t="str">
         <v>圆钩</v>
@@ -17378,7 +17378,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D387" t="str">
-        <v>Big Cat Circle | 3/0 | 25 pack</v>
+        <v>3/0 | 25 pack</v>
       </c>
       <c r="E387" t="str">
         <v>圆钩</v>
@@ -17419,7 +17419,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D388" t="str">
-        <v>Big Cat Circle | 3/0 | 3 pack</v>
+        <v>3/0 | 3 pack</v>
       </c>
       <c r="E388" t="str">
         <v>圆钩</v>
@@ -17460,7 +17460,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D389" t="str">
-        <v>Big Cat Circle | 3/0 | 5 pack</v>
+        <v>3/0 | 5 pack</v>
       </c>
       <c r="E389" t="str">
         <v>圆钩</v>
@@ -17501,7 +17501,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D390" t="str">
-        <v>Big Cat Circle | 3/0 | 6 pack</v>
+        <v>3/0 | 6 pack</v>
       </c>
       <c r="E390" t="str">
         <v>圆钩</v>
@@ -17542,7 +17542,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D391" t="str">
-        <v>Big Cat Circle | 4/0 | 25 pack</v>
+        <v>4/0 | 25 pack</v>
       </c>
       <c r="E391" t="str">
         <v>圆钩</v>
@@ -17583,7 +17583,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D392" t="str">
-        <v>Big Cat Circle | 4/0 | 3 pack</v>
+        <v>4/0 | 3 pack</v>
       </c>
       <c r="E392" t="str">
         <v>圆钩</v>
@@ -17624,7 +17624,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D393" t="str">
-        <v>Big Cat Circle | 4/0 | 5 pack</v>
+        <v>4/0 | 5 pack</v>
       </c>
       <c r="E393" t="str">
         <v>圆钩</v>
@@ -17665,7 +17665,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D394" t="str">
-        <v>Big Cat Circle | 4/0 | 6 pack</v>
+        <v>4/0 | 6 pack</v>
       </c>
       <c r="E394" t="str">
         <v>圆钩</v>
@@ -17706,7 +17706,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D395" t="str">
-        <v>Big Cat Circle | 5/0 | 25 pack</v>
+        <v>5/0 | 25 pack</v>
       </c>
       <c r="E395" t="str">
         <v>圆钩</v>
@@ -17747,7 +17747,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D396" t="str">
-        <v>Big Cat Circle | 5/0 | 3 pack</v>
+        <v>5/0 | 3 pack</v>
       </c>
       <c r="E396" t="str">
         <v>圆钩</v>
@@ -17788,7 +17788,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D397" t="str">
-        <v>Big Cat Circle | 5/0 | 5 pack</v>
+        <v>5/0 | 5 pack</v>
       </c>
       <c r="E397" t="str">
         <v>圆钩</v>
@@ -17829,7 +17829,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D398" t="str">
-        <v>Big Cat Circle | 5/0 | 6 pack</v>
+        <v>5/0 | 6 pack</v>
       </c>
       <c r="E398" t="str">
         <v>圆钩</v>
@@ -17870,7 +17870,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D399" t="str">
-        <v>Big Cat Circle | 6/0 | 25 pack</v>
+        <v>6/0 | 25 pack</v>
       </c>
       <c r="E399" t="str">
         <v>圆钩</v>
@@ -17911,7 +17911,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D400" t="str">
-        <v>Big Cat Circle | 6/0 | 3 pack</v>
+        <v>6/0 | 3 pack</v>
       </c>
       <c r="E400" t="str">
         <v>圆钩</v>
@@ -17952,7 +17952,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D401" t="str">
-        <v>Big Cat Circle | 6/0 | 5 pack</v>
+        <v>6/0 | 5 pack</v>
       </c>
       <c r="E401" t="str">
         <v>圆钩</v>
@@ -17993,7 +17993,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D402" t="str">
-        <v>Big Cat Circle | 6/0 | 6 pack</v>
+        <v>6/0 | 6 pack</v>
       </c>
       <c r="E402" t="str">
         <v>圆钩</v>
@@ -18034,7 +18034,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D403" t="str">
-        <v>Big Cat Circle | 7/0 | 25 pack</v>
+        <v>7/0 | 25 pack</v>
       </c>
       <c r="E403" t="str">
         <v>圆钩</v>
@@ -18075,7 +18075,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D404" t="str">
-        <v>Big Cat Circle | 7/0 | 3 pack</v>
+        <v>7/0 | 3 pack</v>
       </c>
       <c r="E404" t="str">
         <v>圆钩</v>
@@ -18116,7 +18116,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D405" t="str">
-        <v>Big Cat Circle | 7/0 | 5 pack</v>
+        <v>7/0 | 5 pack</v>
       </c>
       <c r="E405" t="str">
         <v>圆钩</v>
@@ -18157,7 +18157,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D406" t="str">
-        <v>Big Cat Circle | 7/0 | 6 pack</v>
+        <v>7/0 | 6 pack</v>
       </c>
       <c r="E406" t="str">
         <v>圆钩</v>
@@ -18198,7 +18198,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D407" t="str">
-        <v>Big Cat Circle | 8/0 | 25 pack</v>
+        <v>8/0 | 25 pack</v>
       </c>
       <c r="E407" t="str">
         <v>圆钩</v>
@@ -18239,7 +18239,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D408" t="str">
-        <v>Big Cat Circle | 8/0 | 3 pack</v>
+        <v>8/0 | 3 pack</v>
       </c>
       <c r="E408" t="str">
         <v>圆钩</v>
@@ -18280,7 +18280,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D409" t="str">
-        <v>Big Cat Circle | 8/0 | 5 pack</v>
+        <v>8/0 | 5 pack</v>
       </c>
       <c r="E409" t="str">
         <v>圆钩</v>
@@ -18321,7 +18321,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D410" t="str">
-        <v>Big Cat Circle | 8/0 | 6 pack</v>
+        <v>8/0 | 6 pack</v>
       </c>
       <c r="E410" t="str">
         <v>圆钩</v>
@@ -18362,7 +18362,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D411" t="str">
-        <v>Big Cat Circle | 10/0 | 25 pack</v>
+        <v>10/0 | 25 pack</v>
       </c>
       <c r="E411" t="str">
         <v>圆钩</v>
@@ -18403,7 +18403,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D412" t="str">
-        <v>Big Cat Circle | 10/0 | 3 pack</v>
+        <v>10/0 | 3 pack</v>
       </c>
       <c r="E412" t="str">
         <v>圆钩</v>
@@ -18444,7 +18444,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D413" t="str">
-        <v>Big Cat Circle | 10/0 | 5 pack</v>
+        <v>10/0 | 5 pack</v>
       </c>
       <c r="E413" t="str">
         <v>圆钩</v>
@@ -18485,7 +18485,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D414" t="str">
-        <v>Big Cat Circle | 10/0 | 6 pack</v>
+        <v>10/0 | 6 pack</v>
       </c>
       <c r="E414" t="str">
         <v>圆钩</v>
@@ -18526,7 +18526,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D415" t="str">
-        <v>Big Cat Circle | 12/0 | 25 pack</v>
+        <v>12/0 | 25 pack</v>
       </c>
       <c r="E415" t="str">
         <v>圆钩</v>
@@ -18567,7 +18567,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D416" t="str">
-        <v>Big Cat Circle | 12/0 | 3 pack</v>
+        <v>12/0 | 3 pack</v>
       </c>
       <c r="E416" t="str">
         <v>圆钩</v>
@@ -18608,7 +18608,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D417" t="str">
-        <v>Big Cat Circle | 12/0 | 5 pack</v>
+        <v>12/0 | 5 pack</v>
       </c>
       <c r="E417" t="str">
         <v>圆钩</v>
@@ -18649,7 +18649,7 @@
         <v>Gamakatsu</v>
       </c>
       <c r="D418" t="str">
-        <v>Big Cat Circle | 12/0 | 6 pack</v>
+        <v>12/0 | 6 pack</v>
       </c>
       <c r="E418" t="str">
         <v>圆钩</v>
